--- a/ofsted_csc_ilacs_overview.xlsx
+++ b/ofsted_csc_ilacs_overview.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2923" uniqueCount="1432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2923" uniqueCount="1433">
   <si>
     <t>80426</t>
   </si>
@@ -1150,13 +1150,667 @@
     <t>east riding of yorkshire</t>
   </si>
   <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50212242</t>
+    <t>https://files.ofsted.gov.uk/v1/file/50316051</t>
+  </si>
+  <si>
+    <t>jenny -ellen scotland</t>
+  </si>
+  <si>
+    <t>12/06/2026</t>
+  </si>
+  <si>
+    <t>30/10/26</t>
+  </si>
+  <si>
+    <t>80467</t>
+  </si>
+  <si>
+    <t>845</t>
+  </si>
+  <si>
+    <t>E10000011</t>
+  </si>
+  <si>
+    <t>878, 886, 908, 926, 881, 351, 838, 938, 929, 839</t>
+  </si>
+  <si>
+    <t>[(878, 'inadequate'), (886, 'good'), (908, 'good'), (926, 'outstanding'), (881, 'outstanding'), (351, 'requires improvement'), (838, 'outstanding'), (938, 'requires improvement'), (929, 'outstanding'), (839, 'good')]</t>
+  </si>
+  <si>
+    <t>east sussex</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50239111</t>
+  </si>
+  <si>
+    <t>tom anthony</t>
+  </si>
+  <si>
+    <t>11/12/2023</t>
+  </si>
+  <si>
+    <t>15/12/2023</t>
+  </si>
+  <si>
+    <t>06/02/24</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>80468</t>
+  </si>
+  <si>
+    <t>881</t>
+  </si>
+  <si>
+    <t>E10000012</t>
+  </si>
+  <si>
+    <t>886, 938, 916, 802, 935, 850, 937, 933, 303, 865</t>
+  </si>
+  <si>
+    <t>[(886, 'good'), (938, 'requires improvement'), (916, 'good'), (802, 'requires improvement'), (935, 'requires improvement'), (850, 'outstanding'), (937, 'requires improvement'), (933, 'Not reported (2026 framework change)'), (303, 'outstanding'), (865, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>essex</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50225703</t>
+  </si>
+  <si>
+    <t>kendra bell</t>
+  </si>
+  <si>
+    <t>26/06/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
+  </si>
+  <si>
+    <t>11/08/23</t>
+  </si>
+  <si>
+    <t>80469</t>
+  </si>
+  <si>
+    <t>390</t>
+  </si>
+  <si>
+    <t>E08000037</t>
+  </si>
+  <si>
+    <t>841, 357, 393, 372, 808, 840, 807, 394, 332, 384</t>
+  </si>
+  <si>
+    <t>[(841, 'outstanding'), (357, 'inadequate'), (393, 'Not reported (2026 framework change)'), (372, 'outstanding'), (808, 'requires improvement'), (840, 'outstanding'), (807, 'good'), (394, 'outstanding'), (332, 'Not reported (2026 framework change)'), (384, 'good')]</t>
+  </si>
+  <si>
+    <t>gateshead</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50267802</t>
+  </si>
+  <si>
+    <t>06/12/2024</t>
+  </si>
+  <si>
+    <t>80470</t>
+  </si>
+  <si>
+    <t>916</t>
+  </si>
+  <si>
+    <t>E10000013</t>
+  </si>
+  <si>
+    <t>937, 938, 850, 802, 865, 895, 855, 931, 881, 885</t>
+  </si>
+  <si>
+    <t>[(937, 'requires improvement'), (938, 'requires improvement'), (850, 'outstanding'), (802, 'requires improvement'), (865, 'outstanding'), (895, 'inadequate'), (855, 'outstanding'), (931, 'good'), (881, 'outstanding'), (885, 'good')]</t>
+  </si>
+  <si>
+    <t>gloucestershire</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50283717</t>
+  </si>
+  <si>
+    <t>04/08/25</t>
+  </si>
+  <si>
+    <t>80471</t>
+  </si>
+  <si>
+    <t>876</t>
+  </si>
+  <si>
+    <t>E06000006</t>
+  </si>
+  <si>
+    <t>342, 840, 344, 394, 807, 370, 390, 372, 808, 343</t>
+  </si>
+  <si>
+    <t>[(342, 'good'), (840, 'outstanding'), (344, 'requires improvement'), (394, 'outstanding'), (807, 'good'), (370, 'good'), (390, 'good'), (372, 'outstanding'), (808, 'requires improvement'), (343, 'good')]</t>
+  </si>
+  <si>
+    <t>halton</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50252259</t>
+  </si>
+  <si>
+    <t>lisa summers</t>
+  </si>
+  <si>
+    <t>13/05/2024</t>
+  </si>
+  <si>
+    <t>24/05/2024</t>
+  </si>
+  <si>
+    <t>12/07/24</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>80472</t>
+  </si>
+  <si>
+    <t>850</t>
+  </si>
+  <si>
+    <t>E10000014</t>
+  </si>
+  <si>
+    <t>865, 802, 916, 938, 869, 867, 803, 937, 931, 855</t>
+  </si>
+  <si>
+    <t>[(865, 'outstanding'), (802, 'requires improvement'), (916, 'good'), (938, 'requires improvement'), (869, 'good'), (867, 'outstanding'), (803, 'good'), (937, 'requires improvement'), (931, 'good'), (855, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>hampshire</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50253183</t>
+  </si>
+  <si>
+    <t>10/06/2024</t>
+  </si>
+  <si>
+    <t>14/06/2024</t>
+  </si>
+  <si>
+    <t>23/07/24</t>
+  </si>
+  <si>
+    <t>80473</t>
+  </si>
+  <si>
+    <t>805</t>
+  </si>
+  <si>
+    <t>E06000001</t>
+  </si>
+  <si>
+    <t>807, 394, 393, 890, 806, 390, 840, 876, 372, 340</t>
+  </si>
+  <si>
+    <t>[(807, 'good'), (394, 'outstanding'), (393, 'Not reported (2026 framework change)'), (890, 'Not reported (2026 framework change)'), (806, 'Not reported (2026 framework change)'), (390, 'good'), (840, 'outstanding'), (876, 'inadequate'), (372, 'outstanding'), (340, 'inadequate')]</t>
+  </si>
+  <si>
+    <t>hartlepool</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50247208</t>
   </si>
   <si>
     <t>louise walker</t>
   </si>
   <si>
-    <t>30/01/2023</t>
+    <t>18/03/2024</t>
+  </si>
+  <si>
+    <t>22/03/2024</t>
+  </si>
+  <si>
+    <t>80474</t>
+  </si>
+  <si>
+    <t>884</t>
+  </si>
+  <si>
+    <t>E06000019</t>
+  </si>
+  <si>
+    <t>943, 860, 925, 893, 933, 888, 935, 811, 815, 830</t>
+  </si>
+  <si>
+    <t>[(943, 'good'), (860, 'requires improvement'), (925, 'outstanding'), (893, 'outstanding'), (933, 'Not reported (2026 framework change)'), (888, 'Not reported (2026 framework change)'), (935, 'requires improvement'), (811, 'Not reported (2026 framework change)'), (815, 'outstanding'), (830, 'good')]</t>
+  </si>
+  <si>
+    <t>herefordshire</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50293401</t>
+  </si>
+  <si>
+    <t>10/11/2025</t>
+  </si>
+  <si>
+    <t>21/11/2025</t>
+  </si>
+  <si>
+    <t>12/01/26</t>
+  </si>
+  <si>
+    <t>80475</t>
+  </si>
+  <si>
+    <t>919</t>
+  </si>
+  <si>
+    <t>E10000015</t>
+  </si>
+  <si>
+    <t>931, 825, 873, 867, 938, 305, 850, 358, 916, 869</t>
+  </si>
+  <si>
+    <t>[(931, 'good'), (825, 'requires improvement'), (873, 'requires improvement'), (867, 'outstanding'), (938, 'requires improvement'), (305, 'outstanding'), (850, 'outstanding'), (358, 'Not reported (2026 framework change)'), (916, 'good'), (869, 'good')]</t>
+  </si>
+  <si>
+    <t>hertfordshire</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50309681</t>
+  </si>
+  <si>
+    <t>13/07/2026</t>
+  </si>
+  <si>
+    <t>data_unreadable</t>
+  </si>
+  <si>
+    <t>80419</t>
+  </si>
+  <si>
+    <t>921</t>
+  </si>
+  <si>
+    <t>E06000046</t>
+  </si>
+  <si>
+    <t>357, 908, 926, 880, 879, 350, 929, 372, 354, 351</t>
+  </si>
+  <si>
+    <t>[(357, 'inadequate'), (908, 'good'), (926, 'outstanding'), (880, 'good'), (879, 'requires improvement'), (350, 'good'), (929, 'outstanding'), (372, 'outstanding'), (354, 'requires improvement'), (351, 'requires improvement')]</t>
+  </si>
+  <si>
+    <t>isle of wight</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50235617</t>
+  </si>
+  <si>
+    <t>03/11/2023</t>
+  </si>
+  <si>
+    <t>15/12/23</t>
+  </si>
+  <si>
+    <t>80476</t>
+  </si>
+  <si>
+    <t>886</t>
+  </si>
+  <si>
+    <t>E10000016</t>
+  </si>
+  <si>
+    <t>881, 845, 878, 303, 935, 926, 891, 938, 822, 933</t>
+  </si>
+  <si>
+    <t>[(881, 'outstanding'), (845, 'good'), (878, 'inadequate'), (303, 'outstanding'), (935, 'requires improvement'), (926, 'outstanding'), (891, 'good'), (938, 'requires improvement'), (822, 'requires improvement'), (933, 'Not reported (2026 framework change)')]</t>
+  </si>
+  <si>
+    <t>kent</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50294428</t>
+  </si>
+  <si>
+    <t>steve lowe</t>
+  </si>
+  <si>
+    <t>03/11/2025</t>
+  </si>
+  <si>
+    <t>07/11/2025</t>
+  </si>
+  <si>
+    <t>02/02/26</t>
+  </si>
+  <si>
+    <t>80477</t>
+  </si>
+  <si>
+    <t>810</t>
+  </si>
+  <si>
+    <t>E06000010</t>
+  </si>
+  <si>
+    <t>333, 336, 861, 335, 812, 354, 806, 371, 831, 372</t>
+  </si>
+  <si>
+    <t>[(333, 'good'), (336, 'good'), (861, 'requires improvement'), (335, 'outstanding'), (812, 'good'), (354, 'requires improvement'), (806, 'Not reported (2026 framework change)'), (371, 'good'), (831, 'outstanding'), (372, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>kingston upon hull</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50301678</t>
+  </si>
+  <si>
+    <t>02/03/2026</t>
+  </si>
+  <si>
+    <t>80478</t>
+  </si>
+  <si>
+    <t>382</t>
+  </si>
+  <si>
+    <t>E08000034</t>
+  </si>
+  <si>
+    <t>373, 357, 851, 831, 879, 354, 351, 384, 908, 390</t>
+  </si>
+  <si>
+    <t>[(373, 'good'), (357, 'inadequate'), (851, 'Not reported (2026 framework change)'), (831, 'outstanding'), (879, 'requires improvement'), (354, 'requires improvement'), (351, 'requires improvement'), (384, 'good'), (908, 'good'), (390, 'good')]</t>
+  </si>
+  <si>
+    <t>kirklees</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50255618</t>
+  </si>
+  <si>
+    <t>rachel griffiths</t>
+  </si>
+  <si>
+    <t>08/07/2024</t>
+  </si>
+  <si>
+    <t>80479</t>
+  </si>
+  <si>
+    <t>340</t>
+  </si>
+  <si>
+    <t>E08000011</t>
+  </si>
+  <si>
+    <t>342, 876, 394, 805, 807, 343, 344, 393, 840, 341</t>
+  </si>
+  <si>
+    <t>[(342, 'good'), (876, 'inadequate'), (394, 'outstanding'), (805, 'outstanding'), (807, 'good'), (343, 'good'), (344, 'requires improvement'), (393, 'Not reported (2026 framework change)'), (840, 'outstanding'), (341, 'Not reported (2026 framework change)')]</t>
+  </si>
+  <si>
+    <t>knowsley</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50267008</t>
+  </si>
+  <si>
+    <t>rebekah tucker</t>
+  </si>
+  <si>
+    <t>18/11/2024</t>
+  </si>
+  <si>
+    <t>29/11/2024</t>
+  </si>
+  <si>
+    <t>20/01/25</t>
+  </si>
+  <si>
+    <t>80480</t>
+  </si>
+  <si>
+    <t>888</t>
+  </si>
+  <si>
+    <t>E10000017</t>
+  </si>
+  <si>
+    <t>925, 351, 332, 884, 841, 808, 384, 891, 929, 359</t>
+  </si>
+  <si>
+    <t>[(925, 'outstanding'), (351, 'requires improvement'), (332, 'Not reported (2026 framework change)'), (884, 'good'), (841, 'outstanding'), (808, 'requires improvement'), (384, 'good'), (891, 'good'), (929, 'outstanding'), (359, 'good')]</t>
+  </si>
+  <si>
+    <t>lancashire</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50309857</t>
+  </si>
+  <si>
+    <t>11/05/2026</t>
+  </si>
+  <si>
+    <t>22/05/2026</t>
+  </si>
+  <si>
+    <t>20/08/26</t>
+  </si>
+  <si>
+    <t>80481</t>
+  </si>
+  <si>
+    <t>383</t>
+  </si>
+  <si>
+    <t>E08000035</t>
+  </si>
+  <si>
+    <t>851, 882, 373, 826, 382, 355, 801, 852, 306, 839</t>
+  </si>
+  <si>
+    <t>[(851, 'Not reported (2026 framework change)'), (882, 'good'), (373, 'good'), (826, 'good'), (382, 'good'), (355, 'good'), (801, 'requires improvement'), (852, 'good'), (306, 'good'), (839, 'good')]</t>
+  </si>
+  <si>
+    <t>leeds</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50284438</t>
+  </si>
+  <si>
+    <t>30/06/2025</t>
+  </si>
+  <si>
+    <t>04/07/2025</t>
+  </si>
+  <si>
+    <t>12/08/25</t>
+  </si>
+  <si>
+    <t>80482</t>
+  </si>
+  <si>
+    <t>856</t>
+  </si>
+  <si>
+    <t>E06000016</t>
+  </si>
+  <si>
+    <t>821, 871, 304, 316, 333, 380, 307, 313, 330, 889</t>
+  </si>
+  <si>
+    <t>[(821, 'good'), (871, 'Not reported (2026 framework change)'), (304, 'Not reported (2026 framework change)'), (316, 'outstanding'), (333, 'good'), (380, 'requires improvement'), (307, 'good'), (313, 'good'), (330, 'good'), (889, 'good')]</t>
+  </si>
+  <si>
+    <t>leicester</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50267800</t>
+  </si>
+  <si>
+    <t>80483</t>
+  </si>
+  <si>
+    <t>855</t>
+  </si>
+  <si>
+    <t>E10000018</t>
+  </si>
+  <si>
+    <t>916, 803, 937, 802, 850, 865, 933, 938, 811, 891</t>
+  </si>
+  <si>
+    <t>[(916, 'good'), (803, 'good'), (937, 'requires improvement'), (802, 'requires improvement'), (850, 'outstanding'), (865, 'outstanding'), (933, 'Not reported (2026 framework change)'), (938, 'requires improvement'), (811, 'Not reported (2026 framework change)'), (891, 'good')]</t>
+  </si>
+  <si>
+    <t>leicestershire</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50252253</t>
+  </si>
+  <si>
+    <t>22/04/2024</t>
+  </si>
+  <si>
+    <t>03/05/2024</t>
+  </si>
+  <si>
+    <t>80484</t>
+  </si>
+  <si>
+    <t>925</t>
+  </si>
+  <si>
+    <t>E10000019</t>
+  </si>
+  <si>
+    <t>888, 384, 884, 813, 926, 935, 332, 940, 830, 933</t>
+  </si>
+  <si>
+    <t>[(888, 'Not reported (2026 framework change)'), (384, 'good'), (884, 'good'), (813, 'outstanding'), (926, 'outstanding'), (935, 'requires improvement'), (332, 'Not reported (2026 framework change)'), (940, 'Not reported (2026 framework change)'), (830, 'good'), (933, 'Not reported (2026 framework change)')]</t>
+  </si>
+  <si>
+    <t>lincolnshire</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50219720</t>
+  </si>
+  <si>
+    <t>24/04/2023</t>
+  </si>
+  <si>
+    <t>28/04/2023</t>
+  </si>
+  <si>
+    <t>14/06/23</t>
+  </si>
+  <si>
+    <t>80485</t>
+  </si>
+  <si>
+    <t>341</t>
+  </si>
+  <si>
+    <t>E08000012</t>
+  </si>
+  <si>
+    <t>890, 805, 806, 355, 393, 340, 394, 391, 807, 354</t>
+  </si>
+  <si>
+    <t>[(890, 'Not reported (2026 framework change)'), (805, 'outstanding'), (806, 'Not reported (2026 framework change)'), (355, 'good'), (393, 'Not reported (2026 framework change)'), (340, 'inadequate'), (394, 'outstanding'), (391, 'good'), (807, 'good'), (354, 'requires improvement')]</t>
+  </si>
+  <si>
+    <t>liverpool</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50306784</t>
+  </si>
+  <si>
+    <t>07/07/26</t>
+  </si>
+  <si>
+    <t>80486</t>
+  </si>
+  <si>
+    <t>301</t>
+  </si>
+  <si>
+    <t>E09000002</t>
+  </si>
+  <si>
+    <t>308, 821, 313, 333, 336, 307, 304, 312, 874, 203</t>
+  </si>
+  <si>
+    <t>[(308, 'good'), (821, 'good'), (313, 'good'), (333, 'good'), (336, 'good'), (307, 'good'), (304, 'Not reported (2026 framework change)'), (312, 'outstanding'), (874, 'inadequate'), (203, 'outstanding')]</t>
+  </si>
+  <si>
+    <t>barking and dagenham</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50227183</t>
+  </si>
+  <si>
+    <t>10/07/2023</t>
+  </si>
+  <si>
+    <t>21/07/2023</t>
+  </si>
+  <si>
+    <t>04/09/23</t>
+  </si>
+  <si>
+    <t>80487</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>E09000003</t>
+  </si>
+  <si>
+    <t>320, 870, 310, 317, 315, 306, 209, 312, 309, 307</t>
+  </si>
+  <si>
+    <t>[(320, 'good'), (870, 'requires improvement'), (310, 'inadequate'), (317, 'outstanding'), (315, 'outstanding'), (306, 'good'), (209, 'good'), (312, 'outstanding'), (309, 'outstanding'), (307, 'good')]</t>
+  </si>
+  <si>
+    <t>barnet</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50253182</t>
+  </si>
+  <si>
+    <t>80488</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>E09000004</t>
+  </si>
+  <si>
+    <t>311, 822, 886, 881, 883, 887, 826, 866, 839, 351</t>
+  </si>
+  <si>
+    <t>[(311, 'inadequate'), (822, 'requires improvement'), (886, 'good'), (881, 'outstanding'), (883, 'outstanding'), (887, 'good'), (826, 'good'), (866, 'inadequate'), (839, 'good'), (351, 'requires improvement')]</t>
+  </si>
+  <si>
+    <t>bexley</t>
+  </si>
+  <si>
+    <t>https://files.ofsted.gov.uk/v1/file/50212243</t>
+  </si>
+  <si>
+    <t>06/02/2023</t>
   </si>
   <si>
     <t>10/02/2023</t>
@@ -1165,654 +1819,6 @@
     <t>24/03/23</t>
   </si>
   <si>
-    <t>80467</t>
-  </si>
-  <si>
-    <t>845</t>
-  </si>
-  <si>
-    <t>E10000011</t>
-  </si>
-  <si>
-    <t>878, 886, 908, 926, 881, 351, 838, 938, 929, 839</t>
-  </si>
-  <si>
-    <t>[(878, 'inadequate'), (886, 'good'), (908, 'good'), (926, 'outstanding'), (881, 'outstanding'), (351, 'requires improvement'), (838, 'outstanding'), (938, 'requires improvement'), (929, 'outstanding'), (839, 'good')]</t>
-  </si>
-  <si>
-    <t>east sussex</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50239111</t>
-  </si>
-  <si>
-    <t>tom anthony</t>
-  </si>
-  <si>
-    <t>11/12/2023</t>
-  </si>
-  <si>
-    <t>15/12/2023</t>
-  </si>
-  <si>
-    <t>06/02/24</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>80468</t>
-  </si>
-  <si>
-    <t>881</t>
-  </si>
-  <si>
-    <t>E10000012</t>
-  </si>
-  <si>
-    <t>886, 938, 916, 802, 935, 850, 937, 933, 303, 865</t>
-  </si>
-  <si>
-    <t>[(886, 'good'), (938, 'requires improvement'), (916, 'good'), (802, 'requires improvement'), (935, 'requires improvement'), (850, 'outstanding'), (937, 'requires improvement'), (933, 'Not reported (2026 framework change)'), (303, 'outstanding'), (865, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>essex</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50225703</t>
-  </si>
-  <si>
-    <t>kendra bell</t>
-  </si>
-  <si>
-    <t>26/06/2023</t>
-  </si>
-  <si>
-    <t>30/06/2023</t>
-  </si>
-  <si>
-    <t>11/08/23</t>
-  </si>
-  <si>
-    <t>80469</t>
-  </si>
-  <si>
-    <t>390</t>
-  </si>
-  <si>
-    <t>E08000037</t>
-  </si>
-  <si>
-    <t>841, 357, 393, 372, 808, 840, 807, 394, 332, 384</t>
-  </si>
-  <si>
-    <t>[(841, 'outstanding'), (357, 'inadequate'), (393, 'Not reported (2026 framework change)'), (372, 'outstanding'), (808, 'requires improvement'), (840, 'outstanding'), (807, 'good'), (394, 'outstanding'), (332, 'Not reported (2026 framework change)'), (384, 'good')]</t>
-  </si>
-  <si>
-    <t>gateshead</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50267802</t>
-  </si>
-  <si>
-    <t>06/12/2024</t>
-  </si>
-  <si>
-    <t>80470</t>
-  </si>
-  <si>
-    <t>916</t>
-  </si>
-  <si>
-    <t>E10000013</t>
-  </si>
-  <si>
-    <t>937, 938, 850, 802, 865, 895, 855, 931, 881, 885</t>
-  </si>
-  <si>
-    <t>[(937, 'requires improvement'), (938, 'requires improvement'), (850, 'outstanding'), (802, 'requires improvement'), (865, 'outstanding'), (895, 'inadequate'), (855, 'outstanding'), (931, 'good'), (881, 'outstanding'), (885, 'good')]</t>
-  </si>
-  <si>
-    <t>gloucestershire</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50283717</t>
-  </si>
-  <si>
-    <t>04/08/25</t>
-  </si>
-  <si>
-    <t>80471</t>
-  </si>
-  <si>
-    <t>876</t>
-  </si>
-  <si>
-    <t>E06000006</t>
-  </si>
-  <si>
-    <t>342, 840, 344, 394, 807, 370, 390, 372, 808, 343</t>
-  </si>
-  <si>
-    <t>[(342, 'good'), (840, 'outstanding'), (344, 'requires improvement'), (394, 'outstanding'), (807, 'good'), (370, 'good'), (390, 'good'), (372, 'outstanding'), (808, 'requires improvement'), (343, 'good')]</t>
-  </si>
-  <si>
-    <t>halton</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50252259</t>
-  </si>
-  <si>
-    <t>lisa summers</t>
-  </si>
-  <si>
-    <t>13/05/2024</t>
-  </si>
-  <si>
-    <t>24/05/2024</t>
-  </si>
-  <si>
-    <t>12/07/24</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>80472</t>
-  </si>
-  <si>
-    <t>850</t>
-  </si>
-  <si>
-    <t>E10000014</t>
-  </si>
-  <si>
-    <t>865, 802, 916, 938, 869, 867, 803, 937, 931, 855</t>
-  </si>
-  <si>
-    <t>[(865, 'outstanding'), (802, 'requires improvement'), (916, 'good'), (938, 'requires improvement'), (869, 'good'), (867, 'outstanding'), (803, 'good'), (937, 'requires improvement'), (931, 'good'), (855, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>hampshire</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50253183</t>
-  </si>
-  <si>
-    <t>10/06/2024</t>
-  </si>
-  <si>
-    <t>14/06/2024</t>
-  </si>
-  <si>
-    <t>23/07/24</t>
-  </si>
-  <si>
-    <t>80473</t>
-  </si>
-  <si>
-    <t>805</t>
-  </si>
-  <si>
-    <t>E06000001</t>
-  </si>
-  <si>
-    <t>807, 394, 393, 890, 806, 390, 840, 876, 372, 340</t>
-  </si>
-  <si>
-    <t>[(807, 'good'), (394, 'outstanding'), (393, 'Not reported (2026 framework change)'), (890, 'Not reported (2026 framework change)'), (806, 'Not reported (2026 framework change)'), (390, 'good'), (840, 'outstanding'), (876, 'inadequate'), (372, 'outstanding'), (340, 'inadequate')]</t>
-  </si>
-  <si>
-    <t>hartlepool</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50247208</t>
-  </si>
-  <si>
-    <t>18/03/2024</t>
-  </si>
-  <si>
-    <t>22/03/2024</t>
-  </si>
-  <si>
-    <t>80474</t>
-  </si>
-  <si>
-    <t>884</t>
-  </si>
-  <si>
-    <t>E06000019</t>
-  </si>
-  <si>
-    <t>943, 860, 925, 893, 933, 888, 935, 811, 815, 830</t>
-  </si>
-  <si>
-    <t>[(943, 'good'), (860, 'requires improvement'), (925, 'outstanding'), (893, 'outstanding'), (933, 'Not reported (2026 framework change)'), (888, 'Not reported (2026 framework change)'), (935, 'requires improvement'), (811, 'good'), (815, 'outstanding'), (830, 'good')]</t>
-  </si>
-  <si>
-    <t>herefordshire</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50293401</t>
-  </si>
-  <si>
-    <t>10/11/2025</t>
-  </si>
-  <si>
-    <t>21/11/2025</t>
-  </si>
-  <si>
-    <t>12/01/26</t>
-  </si>
-  <si>
-    <t>80475</t>
-  </si>
-  <si>
-    <t>919</t>
-  </si>
-  <si>
-    <t>E10000015</t>
-  </si>
-  <si>
-    <t>931, 825, 873, 867, 938, 305, 850, 358, 916, 869</t>
-  </si>
-  <si>
-    <t>[(931, 'good'), (825, 'requires improvement'), (873, 'requires improvement'), (867, 'outstanding'), (938, 'requires improvement'), (305, 'outstanding'), (850, 'outstanding'), (358, 'Not reported (2026 framework change)'), (916, 'good'), (869, 'good')]</t>
-  </si>
-  <si>
-    <t>hertfordshire</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50309681</t>
-  </si>
-  <si>
-    <t>13/07/2026</t>
-  </si>
-  <si>
-    <t>data_unreadable</t>
-  </si>
-  <si>
-    <t>80419</t>
-  </si>
-  <si>
-    <t>921</t>
-  </si>
-  <si>
-    <t>E06000046</t>
-  </si>
-  <si>
-    <t>357, 908, 926, 880, 879, 350, 929, 372, 354, 351</t>
-  </si>
-  <si>
-    <t>[(357, 'inadequate'), (908, 'good'), (926, 'outstanding'), (880, 'good'), (879, 'requires improvement'), (350, 'good'), (929, 'outstanding'), (372, 'outstanding'), (354, 'requires improvement'), (351, 'requires improvement')]</t>
-  </si>
-  <si>
-    <t>isle of wight</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50235617</t>
-  </si>
-  <si>
-    <t>03/11/2023</t>
-  </si>
-  <si>
-    <t>15/12/23</t>
-  </si>
-  <si>
-    <t>80476</t>
-  </si>
-  <si>
-    <t>886</t>
-  </si>
-  <si>
-    <t>E10000016</t>
-  </si>
-  <si>
-    <t>881, 845, 878, 303, 935, 926, 891, 938, 822, 933</t>
-  </si>
-  <si>
-    <t>[(881, 'outstanding'), (845, 'good'), (878, 'inadequate'), (303, 'outstanding'), (935, 'requires improvement'), (926, 'outstanding'), (891, 'good'), (938, 'requires improvement'), (822, 'requires improvement'), (933, 'Not reported (2026 framework change)')]</t>
-  </si>
-  <si>
-    <t>kent</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50294428</t>
-  </si>
-  <si>
-    <t>steve lowe</t>
-  </si>
-  <si>
-    <t>03/11/2025</t>
-  </si>
-  <si>
-    <t>07/11/2025</t>
-  </si>
-  <si>
-    <t>02/02/26</t>
-  </si>
-  <si>
-    <t>80477</t>
-  </si>
-  <si>
-    <t>810</t>
-  </si>
-  <si>
-    <t>E06000010</t>
-  </si>
-  <si>
-    <t>333, 336, 861, 335, 812, 354, 806, 371, 831, 372</t>
-  </si>
-  <si>
-    <t>[(333, 'good'), (336, 'good'), (861, 'requires improvement'), (335, 'outstanding'), (812, 'good'), (354, 'requires improvement'), (806, 'Not reported (2026 framework change)'), (371, 'good'), (831, 'outstanding'), (372, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>kingston upon hull</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50301678</t>
-  </si>
-  <si>
-    <t>02/03/2026</t>
-  </si>
-  <si>
-    <t>80478</t>
-  </si>
-  <si>
-    <t>382</t>
-  </si>
-  <si>
-    <t>E08000034</t>
-  </si>
-  <si>
-    <t>373, 357, 851, 831, 879, 354, 351, 384, 908, 390</t>
-  </si>
-  <si>
-    <t>[(373, 'good'), (357, 'inadequate'), (851, 'Not reported (2026 framework change)'), (831, 'outstanding'), (879, 'requires improvement'), (354, 'requires improvement'), (351, 'requires improvement'), (384, 'good'), (908, 'good'), (390, 'good')]</t>
-  </si>
-  <si>
-    <t>kirklees</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50255618</t>
-  </si>
-  <si>
-    <t>rachel griffiths</t>
-  </si>
-  <si>
-    <t>08/07/2024</t>
-  </si>
-  <si>
-    <t>80479</t>
-  </si>
-  <si>
-    <t>340</t>
-  </si>
-  <si>
-    <t>E08000011</t>
-  </si>
-  <si>
-    <t>342, 876, 394, 805, 807, 343, 344, 393, 840, 341</t>
-  </si>
-  <si>
-    <t>[(342, 'good'), (876, 'inadequate'), (394, 'outstanding'), (805, 'outstanding'), (807, 'good'), (343, 'good'), (344, 'requires improvement'), (393, 'Not reported (2026 framework change)'), (840, 'outstanding'), (341, 'Not reported (2026 framework change)')]</t>
-  </si>
-  <si>
-    <t>knowsley</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50267008</t>
-  </si>
-  <si>
-    <t>rebekah tucker</t>
-  </si>
-  <si>
-    <t>18/11/2024</t>
-  </si>
-  <si>
-    <t>29/11/2024</t>
-  </si>
-  <si>
-    <t>20/01/25</t>
-  </si>
-  <si>
-    <t>80480</t>
-  </si>
-  <si>
-    <t>888</t>
-  </si>
-  <si>
-    <t>E10000017</t>
-  </si>
-  <si>
-    <t>925, 351, 332, 884, 841, 808, 384, 891, 929, 359</t>
-  </si>
-  <si>
-    <t>[(925, 'outstanding'), (351, 'requires improvement'), (332, 'Not reported (2026 framework change)'), (884, 'good'), (841, 'outstanding'), (808, 'requires improvement'), (384, 'good'), (891, 'good'), (929, 'outstanding'), (359, 'good')]</t>
-  </si>
-  <si>
-    <t>lancashire</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50309857</t>
-  </si>
-  <si>
-    <t>11/05/2026</t>
-  </si>
-  <si>
-    <t>22/05/2026</t>
-  </si>
-  <si>
-    <t>20/08/26</t>
-  </si>
-  <si>
-    <t>80481</t>
-  </si>
-  <si>
-    <t>383</t>
-  </si>
-  <si>
-    <t>E08000035</t>
-  </si>
-  <si>
-    <t>851, 882, 373, 826, 382, 355, 801, 852, 306, 839</t>
-  </si>
-  <si>
-    <t>[(851, 'Not reported (2026 framework change)'), (882, 'good'), (373, 'good'), (826, 'good'), (382, 'good'), (355, 'good'), (801, 'requires improvement'), (852, 'good'), (306, 'good'), (839, 'good')]</t>
-  </si>
-  <si>
-    <t>leeds</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50284438</t>
-  </si>
-  <si>
-    <t>30/06/2025</t>
-  </si>
-  <si>
-    <t>04/07/2025</t>
-  </si>
-  <si>
-    <t>12/08/25</t>
-  </si>
-  <si>
-    <t>80482</t>
-  </si>
-  <si>
-    <t>856</t>
-  </si>
-  <si>
-    <t>E06000016</t>
-  </si>
-  <si>
-    <t>821, 871, 304, 316, 333, 380, 307, 313, 330, 889</t>
-  </si>
-  <si>
-    <t>[(821, 'good'), (871, 'Not reported (2026 framework change)'), (304, 'Not reported (2026 framework change)'), (316, 'outstanding'), (333, 'good'), (380, 'requires improvement'), (307, 'good'), (313, 'good'), (330, 'good'), (889, 'good')]</t>
-  </si>
-  <si>
-    <t>leicester</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50267800</t>
-  </si>
-  <si>
-    <t>80483</t>
-  </si>
-  <si>
-    <t>855</t>
-  </si>
-  <si>
-    <t>E10000018</t>
-  </si>
-  <si>
-    <t>916, 803, 937, 802, 850, 865, 933, 938, 811, 891</t>
-  </si>
-  <si>
-    <t>[(916, 'good'), (803, 'good'), (937, 'requires improvement'), (802, 'requires improvement'), (850, 'outstanding'), (865, 'outstanding'), (933, 'Not reported (2026 framework change)'), (938, 'requires improvement'), (811, 'good'), (891, 'good')]</t>
-  </si>
-  <si>
-    <t>leicestershire</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50252253</t>
-  </si>
-  <si>
-    <t>22/04/2024</t>
-  </si>
-  <si>
-    <t>03/05/2024</t>
-  </si>
-  <si>
-    <t>80484</t>
-  </si>
-  <si>
-    <t>925</t>
-  </si>
-  <si>
-    <t>E10000019</t>
-  </si>
-  <si>
-    <t>888, 384, 884, 813, 926, 935, 332, 940, 830, 933</t>
-  </si>
-  <si>
-    <t>[(888, 'Not reported (2026 framework change)'), (384, 'good'), (884, 'good'), (813, 'outstanding'), (926, 'outstanding'), (935, 'requires improvement'), (332, 'Not reported (2026 framework change)'), (940, 'Not reported (2026 framework change)'), (830, 'good'), (933, 'Not reported (2026 framework change)')]</t>
-  </si>
-  <si>
-    <t>lincolnshire</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50219720</t>
-  </si>
-  <si>
-    <t>24/04/2023</t>
-  </si>
-  <si>
-    <t>28/04/2023</t>
-  </si>
-  <si>
-    <t>14/06/23</t>
-  </si>
-  <si>
-    <t>80485</t>
-  </si>
-  <si>
-    <t>341</t>
-  </si>
-  <si>
-    <t>E08000012</t>
-  </si>
-  <si>
-    <t>890, 805, 806, 355, 393, 340, 394, 391, 807, 354</t>
-  </si>
-  <si>
-    <t>[(890, 'Not reported (2026 framework change)'), (805, 'outstanding'), (806, 'Not reported (2026 framework change)'), (355, 'good'), (393, 'Not reported (2026 framework change)'), (340, 'inadequate'), (394, 'outstanding'), (391, 'good'), (807, 'good'), (354, 'requires improvement')]</t>
-  </si>
-  <si>
-    <t>liverpool</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50306784</t>
-  </si>
-  <si>
-    <t>07/07/26</t>
-  </si>
-  <si>
-    <t>80486</t>
-  </si>
-  <si>
-    <t>301</t>
-  </si>
-  <si>
-    <t>E09000002</t>
-  </si>
-  <si>
-    <t>308, 821, 313, 333, 336, 307, 304, 312, 874, 203</t>
-  </si>
-  <si>
-    <t>[(308, 'good'), (821, 'good'), (313, 'good'), (333, 'good'), (336, 'good'), (307, 'good'), (304, 'Not reported (2026 framework change)'), (312, 'outstanding'), (874, 'inadequate'), (203, 'outstanding')]</t>
-  </si>
-  <si>
-    <t>barking and dagenham</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50227183</t>
-  </si>
-  <si>
-    <t>10/07/2023</t>
-  </si>
-  <si>
-    <t>21/07/2023</t>
-  </si>
-  <si>
-    <t>04/09/23</t>
-  </si>
-  <si>
-    <t>80487</t>
-  </si>
-  <si>
-    <t>302</t>
-  </si>
-  <si>
-    <t>E09000003</t>
-  </si>
-  <si>
-    <t>320, 870, 310, 317, 315, 306, 209, 312, 309, 307</t>
-  </si>
-  <si>
-    <t>[(320, 'good'), (870, 'requires improvement'), (310, 'inadequate'), (317, 'outstanding'), (315, 'outstanding'), (306, 'good'), (209, 'good'), (312, 'outstanding'), (309, 'outstanding'), (307, 'good')]</t>
-  </si>
-  <si>
-    <t>barnet</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50253182</t>
-  </si>
-  <si>
-    <t>80488</t>
-  </si>
-  <si>
-    <t>303</t>
-  </si>
-  <si>
-    <t>E09000004</t>
-  </si>
-  <si>
-    <t>311, 822, 886, 881, 883, 887, 826, 866, 839, 351</t>
-  </si>
-  <si>
-    <t>[(311, 'inadequate'), (822, 'requires improvement'), (886, 'good'), (881, 'outstanding'), (883, 'outstanding'), (887, 'good'), (826, 'good'), (866, 'inadequate'), (839, 'good'), (351, 'requires improvement')]</t>
-  </si>
-  <si>
-    <t>bexley</t>
-  </si>
-  <si>
-    <t>https://files.ofsted.gov.uk/v1/file/50212243</t>
-  </si>
-  <si>
-    <t>06/02/2023</t>
-  </si>
-  <si>
     <t>80489</t>
   </si>
   <si>
@@ -2242,9 +2248,6 @@
     <t>https://files.ofsted.gov.uk/v1/file/50296623</t>
   </si>
   <si>
-    <t>jenny -ellen scotland</t>
-  </si>
-  <si>
     <t>10/03/26</t>
   </si>
   <si>
@@ -2860,7 +2863,7 @@
     <t>893, 895, 811, 860, 916, 877, 937, 884, 865, 933</t>
   </si>
   <si>
-    <t>[(893, 'outstanding'), (895, 'inadequate'), (811, 'good'), (860, 'requires improvement'), (916, 'good'), (877, 'good'), (937, 'requires improvement'), (884, 'good'), (865, 'outstanding'), (933, 'Not reported (2026 framework change)')]</t>
+    <t>[(893, 'outstanding'), (895, 'inadequate'), (811, 'Not reported (2026 framework change)'), (860, 'requires improvement'), (916, 'good'), (877, 'good'), (937, 'requires improvement'), (884, 'good'), (865, 'outstanding'), (933, 'Not reported (2026 framework change)')]</t>
   </si>
   <si>
     <t>north yorkshire</t>
@@ -3271,7 +3274,7 @@
     <t>865, 815, 893, 895, 850, 823, 916, 855, 869, 811</t>
   </si>
   <si>
-    <t>[(865, 'outstanding'), (815, 'outstanding'), (893, 'outstanding'), (895, 'inadequate'), (850, 'outstanding'), (823, 'good'), (916, 'good'), (855, 'outstanding'), (869, 'good'), (811, 'good')]</t>
+    <t>[(865, 'outstanding'), (815, 'outstanding'), (893, 'outstanding'), (895, 'inadequate'), (850, 'outstanding'), (823, 'good'), (916, 'good'), (855, 'outstanding'), (869, 'good'), (811, 'Not reported (2026 framework change)')]</t>
   </si>
   <si>
     <t>rutland</t>
@@ -3406,7 +3409,7 @@
     <t>815, 933, 860, 811, 838, 884, 830, 885, 943, 916</t>
   </si>
   <si>
-    <t>[(815, 'outstanding'), (933, 'Not reported (2026 framework change)'), (860, 'requires improvement'), (811, 'good'), (838, 'outstanding'), (884, 'good'), (830, 'good'), (885, 'good'), (943, 'good'), (916, 'good')]</t>
+    <t>[(815, 'outstanding'), (933, 'Not reported (2026 framework change)'), (860, 'requires improvement'), (811, 'Not reported (2026 framework change)'), (838, 'outstanding'), (884, 'good'), (830, 'good'), (885, 'good'), (943, 'good'), (916, 'good')]</t>
   </si>
   <si>
     <t>shropshire</t>
@@ -3613,7 +3616,7 @@
     <t>811, 884, 893, 815, 933, 830, 877, 891, 943, 888</t>
   </si>
   <si>
-    <t>[(811, 'good'), (884, 'good'), (893, 'outstanding'), (815, 'outstanding'), (933, 'Not reported (2026 framework change)'), (830, 'good'), (877, 'good'), (891, 'good'), (943, 'good'), (888, 'Not reported (2026 framework change)')]</t>
+    <t>[(811, 'Not reported (2026 framework change)'), (884, 'good'), (893, 'outstanding'), (815, 'outstanding'), (933, 'Not reported (2026 framework change)'), (830, 'good'), (877, 'good'), (891, 'good'), (943, 'good'), (888, 'Not reported (2026 framework change)')]</t>
   </si>
   <si>
     <t>staffordshire</t>
@@ -3949,7 +3952,7 @@
     <t>895, 937, 860, 811, 815, 916, 334, 893, 885, 865</t>
   </si>
   <si>
-    <t>[(895, 'inadequate'), (937, 'requires improvement'), (860, 'requires improvement'), (811, 'good'), (815, 'outstanding'), (916, 'good'), (334, 'good'), (893, 'outstanding'), (885, 'good'), (865, 'outstanding')]</t>
+    <t>[(895, 'inadequate'), (937, 'requires improvement'), (860, 'requires improvement'), (811, 'Not reported (2026 framework change)'), (815, 'outstanding'), (916, 'good'), (334, 'good'), (893, 'outstanding'), (885, 'good'), (865, 'outstanding')]</t>
   </si>
   <si>
     <t>warrington</t>
@@ -4078,7 +4081,7 @@
     <t>884, 942, 860, 893, 811, 815, 925, 933, 935, 830</t>
   </si>
   <si>
-    <t>[(884, 'good'), (942, 'good'), (860, 'requires improvement'), (893, 'outstanding'), (811, 'good'), (815, 'outstanding'), (925, 'outstanding'), (933, 'Not reported (2026 framework change)'), (935, 'requires improvement'), (830, 'good')]</t>
+    <t>[(884, 'good'), (942, 'good'), (860, 'requires improvement'), (893, 'outstanding'), (811, 'Not reported (2026 framework change)'), (815, 'outstanding'), (925, 'outstanding'), (933, 'Not reported (2026 framework change)'), (935, 'requires improvement'), (830, 'good')]</t>
   </si>
   <si>
     <t>westmorland and furness</t>
@@ -4677,64 +4680,64 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -6899,22 +6902,22 @@
         <v>378</v>
       </c>
       <c r="I36" t="s">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="J36" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="K36" t="s">
         <v>379</v>
       </c>
       <c r="L36" t="s">
+        <v>75</v>
+      </c>
+      <c r="M36" t="s">
         <v>380</v>
       </c>
-      <c r="M36" t="s">
+      <c r="N36" t="s">
         <v>381</v>
-      </c>
-      <c r="N36" t="s">
-        <v>382</v>
       </c>
       <c r="O36" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80466_east riding of yorkshire", ".\export_data\inspection_reports\80466_east riding of yorkshire")</f>
@@ -6930,36 +6933,36 @@
         <v>8</v>
       </c>
       <c r="S36" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T36" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:20">
       <c r="A37" t="s">
+        <v>382</v>
+      </c>
+      <c r="B37" t="s">
         <v>383</v>
-      </c>
-      <c r="B37" t="s">
-        <v>384</v>
       </c>
       <c r="C37" t="s">
         <v>100</v>
       </c>
       <c r="D37" t="s">
+        <v>384</v>
+      </c>
+      <c r="E37" t="s">
         <v>385</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>386</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>387</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="I37" t="s">
         <v>8</v>
@@ -6968,16 +6971,16 @@
         <v>9</v>
       </c>
       <c r="K37" t="s">
+        <v>389</v>
+      </c>
+      <c r="L37" t="s">
         <v>390</v>
       </c>
-      <c r="L37" t="s">
+      <c r="M37" t="s">
         <v>391</v>
       </c>
-      <c r="M37" t="s">
+      <c r="N37" t="s">
         <v>392</v>
-      </c>
-      <c r="N37" t="s">
-        <v>393</v>
       </c>
       <c r="O37" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80467_east sussex", ".\export_data\inspection_reports\80467_east sussex")</f>
@@ -6996,33 +6999,33 @@
         <v>8</v>
       </c>
       <c r="T37" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="38" spans="1:20">
       <c r="A38" t="s">
+        <v>394</v>
+      </c>
+      <c r="B38" t="s">
         <v>395</v>
-      </c>
-      <c r="B38" t="s">
-        <v>396</v>
       </c>
       <c r="C38" t="s">
         <v>31</v>
       </c>
       <c r="D38" t="s">
+        <v>396</v>
+      </c>
+      <c r="E38" t="s">
         <v>397</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>398</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>399</v>
       </c>
-      <c r="G38" t="s">
+      <c r="H38" s="2" t="s">
         <v>400</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>401</v>
       </c>
       <c r="I38" t="s">
         <v>78</v>
@@ -7031,16 +7034,16 @@
         <v>9</v>
       </c>
       <c r="K38" t="s">
+        <v>401</v>
+      </c>
+      <c r="L38" t="s">
         <v>402</v>
       </c>
-      <c r="L38" t="s">
+      <c r="M38" t="s">
         <v>403</v>
       </c>
-      <c r="M38" t="s">
+      <c r="N38" t="s">
         <v>404</v>
-      </c>
-      <c r="N38" t="s">
-        <v>405</v>
       </c>
       <c r="O38" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80468_essex", ".\export_data\inspection_reports\80468_essex")</f>
@@ -7064,28 +7067,28 @@
     </row>
     <row r="39" spans="1:20">
       <c r="A39" t="s">
+        <v>405</v>
+      </c>
+      <c r="B39" t="s">
         <v>406</v>
-      </c>
-      <c r="B39" t="s">
-        <v>407</v>
       </c>
       <c r="C39" t="s">
         <v>293</v>
       </c>
       <c r="D39" t="s">
+        <v>407</v>
+      </c>
+      <c r="E39" t="s">
         <v>408</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>409</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>410</v>
       </c>
-      <c r="G39" t="s">
+      <c r="H39" s="2" t="s">
         <v>411</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>412</v>
       </c>
       <c r="I39" t="s">
         <v>8</v>
@@ -7100,7 +7103,7 @@
         <v>95</v>
       </c>
       <c r="M39" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="N39" t="s">
         <v>97</v>
@@ -7127,28 +7130,28 @@
     </row>
     <row r="40" spans="1:20">
       <c r="A40" t="s">
+        <v>413</v>
+      </c>
+      <c r="B40" t="s">
         <v>414</v>
-      </c>
-      <c r="B40" t="s">
-        <v>415</v>
       </c>
       <c r="C40" t="s">
         <v>18</v>
       </c>
       <c r="D40" t="s">
+        <v>415</v>
+      </c>
+      <c r="E40" t="s">
         <v>416</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>417</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>418</v>
       </c>
-      <c r="G40" t="s">
+      <c r="H40" s="2" t="s">
         <v>419</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>420</v>
       </c>
       <c r="I40" t="s">
         <v>8</v>
@@ -7166,7 +7169,7 @@
         <v>151</v>
       </c>
       <c r="N40" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="O40" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80470_gloucestershire", ".\export_data\inspection_reports\80470_gloucestershire")</f>
@@ -7190,28 +7193,28 @@
     </row>
     <row r="41" spans="1:20">
       <c r="A41" t="s">
+        <v>421</v>
+      </c>
+      <c r="B41" t="s">
         <v>422</v>
-      </c>
-      <c r="B41" t="s">
-        <v>423</v>
       </c>
       <c r="C41" t="s">
         <v>56</v>
       </c>
       <c r="D41" t="s">
+        <v>423</v>
+      </c>
+      <c r="E41" t="s">
         <v>424</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>425</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>426</v>
       </c>
-      <c r="G41" t="s">
+      <c r="H41" s="2" t="s">
         <v>427</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>428</v>
       </c>
       <c r="I41" t="s">
         <v>189</v>
@@ -7220,16 +7223,16 @@
         <v>48</v>
       </c>
       <c r="K41" t="s">
+        <v>428</v>
+      </c>
+      <c r="L41" t="s">
         <v>429</v>
       </c>
-      <c r="L41" t="s">
+      <c r="M41" t="s">
         <v>430</v>
       </c>
-      <c r="M41" t="s">
+      <c r="N41" t="s">
         <v>431</v>
-      </c>
-      <c r="N41" t="s">
-        <v>432</v>
       </c>
       <c r="O41" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80471_halton", ".\export_data\inspection_reports\80471_halton")</f>
@@ -7248,33 +7251,33 @@
         <v>189</v>
       </c>
       <c r="T41" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="42" spans="1:20">
       <c r="A42" t="s">
+        <v>433</v>
+      </c>
+      <c r="B42" t="s">
         <v>434</v>
-      </c>
-      <c r="B42" t="s">
-        <v>435</v>
       </c>
       <c r="C42" t="s">
         <v>100</v>
       </c>
       <c r="D42" t="s">
+        <v>435</v>
+      </c>
+      <c r="E42" t="s">
         <v>436</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>437</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>438</v>
       </c>
-      <c r="G42" t="s">
+      <c r="H42" s="2" t="s">
         <v>439</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>440</v>
       </c>
       <c r="I42" t="s">
         <v>78</v>
@@ -7283,16 +7286,16 @@
         <v>9</v>
       </c>
       <c r="K42" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="L42" t="s">
+        <v>440</v>
+      </c>
+      <c r="M42" t="s">
         <v>441</v>
       </c>
-      <c r="M42" t="s">
+      <c r="N42" t="s">
         <v>442</v>
-      </c>
-      <c r="N42" t="s">
-        <v>443</v>
       </c>
       <c r="O42" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80472_hampshire", ".\export_data\inspection_reports\80472_hampshire")</f>
@@ -7316,28 +7319,28 @@
     </row>
     <row r="43" spans="1:20">
       <c r="A43" t="s">
+        <v>443</v>
+      </c>
+      <c r="B43" t="s">
         <v>444</v>
-      </c>
-      <c r="B43" t="s">
-        <v>445</v>
       </c>
       <c r="C43" t="s">
         <v>293</v>
       </c>
       <c r="D43" t="s">
+        <v>445</v>
+      </c>
+      <c r="E43" t="s">
         <v>446</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>447</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>448</v>
       </c>
-      <c r="G43" t="s">
+      <c r="H43" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>450</v>
       </c>
       <c r="I43" t="s">
         <v>78</v>
@@ -7346,7 +7349,7 @@
         <v>9</v>
       </c>
       <c r="K43" t="s">
-        <v>379</v>
+        <v>450</v>
       </c>
       <c r="L43" t="s">
         <v>451</v>
@@ -7374,7 +7377,7 @@
         <v>8</v>
       </c>
       <c r="T43" t="s">
-        <v>15</v>
+        <v>432</v>
       </c>
     </row>
     <row r="44" spans="1:20">
@@ -7626,7 +7629,7 @@
         <v>14</v>
       </c>
       <c r="T47" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="48" spans="1:20">
@@ -7976,7 +7979,7 @@
         <v>9</v>
       </c>
       <c r="K53" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L53" t="s">
         <v>224</v>
@@ -8004,7 +8007,7 @@
         <v>14</v>
       </c>
       <c r="T53" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="54" spans="1:20">
@@ -8048,7 +8051,7 @@
         <v>555</v>
       </c>
       <c r="N54" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="O54" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80483_leicestershire", ".\export_data\inspection_reports\80483_leicestershire")</f>
@@ -8294,13 +8297,13 @@
         <v>106</v>
       </c>
       <c r="L58" t="s">
+        <v>440</v>
+      </c>
+      <c r="M58" t="s">
         <v>441</v>
       </c>
-      <c r="M58" t="s">
+      <c r="N58" t="s">
         <v>442</v>
-      </c>
-      <c r="N58" t="s">
-        <v>443</v>
       </c>
       <c r="O58" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80487_barnet", ".\export_data\inspection_reports\80487_barnet")</f>
@@ -8354,16 +8357,16 @@
         <v>9</v>
       </c>
       <c r="K59" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L59" t="s">
         <v>598</v>
       </c>
       <c r="M59" t="s">
-        <v>381</v>
+        <v>599</v>
       </c>
       <c r="N59" t="s">
-        <v>382</v>
+        <v>600</v>
       </c>
       <c r="O59" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80488_bexley", ".\export_data\inspection_reports\80488_bexley")</f>
@@ -8382,33 +8385,33 @@
         <v>78</v>
       </c>
       <c r="T59" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="60" spans="1:20">
       <c r="A60" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B60" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C60" t="s">
         <v>217</v>
       </c>
       <c r="D60" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E60" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="F60" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="G60" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="I60" t="s">
         <v>73</v>
@@ -8417,16 +8420,16 @@
         <v>9</v>
       </c>
       <c r="K60" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="L60" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="M60" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="N60" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="O60" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80489_brent", ".\export_data\inspection_reports\80489_brent")</f>
@@ -8450,28 +8453,28 @@
     </row>
     <row r="61" spans="1:20">
       <c r="A61" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B61" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C61" t="s">
         <v>217</v>
       </c>
       <c r="D61" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="E61" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="F61" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="G61" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="I61" t="s">
         <v>78</v>
@@ -8480,13 +8483,13 @@
         <v>9</v>
       </c>
       <c r="K61" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="L61" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="M61" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="N61" t="s">
         <v>322</v>
@@ -8513,28 +8516,28 @@
     </row>
     <row r="62" spans="1:20">
       <c r="A62" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B62" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C62" t="s">
         <v>217</v>
       </c>
       <c r="D62" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="E62" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="F62" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="G62" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="I62" t="s">
         <v>78</v>
@@ -8543,7 +8546,7 @@
         <v>9</v>
       </c>
       <c r="K62" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="L62" t="s">
         <v>63</v>
@@ -8576,28 +8579,28 @@
     </row>
     <row r="63" spans="1:20">
       <c r="A63" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B63" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C63" t="s">
         <v>217</v>
       </c>
       <c r="D63" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E63" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="F63" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="G63" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="I63" t="s">
         <v>8</v>
@@ -8609,13 +8612,13 @@
         <v>223</v>
       </c>
       <c r="L63" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="M63" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="N63" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="O63" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80492_croydon", ".\export_data\inspection_reports\80492_croydon")</f>
@@ -8639,28 +8642,28 @@
     </row>
     <row r="64" spans="1:20">
       <c r="A64" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B64" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C64" t="s">
         <v>217</v>
       </c>
       <c r="D64" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="E64" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="F64" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="G64" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="I64" t="s">
         <v>8</v>
@@ -8669,7 +8672,7 @@
         <v>48</v>
       </c>
       <c r="K64" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L64" t="s">
         <v>554</v>
@@ -8678,7 +8681,7 @@
         <v>555</v>
       </c>
       <c r="N64" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="O64" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80493_ealing", ".\export_data\inspection_reports\80493_ealing")</f>
@@ -8697,33 +8700,33 @@
         <v>8</v>
       </c>
       <c r="T64" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="65" spans="1:20">
       <c r="A65" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B65" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C65" t="s">
         <v>217</v>
       </c>
       <c r="D65" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E65" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="F65" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="G65" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="I65" t="s">
         <v>8</v>
@@ -8735,13 +8738,13 @@
         <v>223</v>
       </c>
       <c r="L65" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="M65" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="N65" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="O65" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80494_enfield", ".\export_data\inspection_reports\80494_enfield")</f>
@@ -8765,28 +8768,28 @@
     </row>
     <row r="66" spans="1:20">
       <c r="A66" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B66" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C66" t="s">
         <v>217</v>
       </c>
       <c r="D66" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="E66" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="F66" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="G66" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="I66" t="s">
         <v>78</v>
@@ -8795,16 +8798,16 @@
         <v>9</v>
       </c>
       <c r="K66" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L66" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="M66" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="N66" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="O66" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80495_greenwich", ".\export_data\inspection_reports\80495_greenwich")</f>
@@ -8823,33 +8826,33 @@
         <v>78</v>
       </c>
       <c r="T66" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="67" spans="1:20">
       <c r="A67" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B67" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="C67" t="s">
         <v>217</v>
       </c>
       <c r="D67" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E67" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="F67" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="G67" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="I67" t="s">
         <v>8</v>
@@ -8864,10 +8867,10 @@
         <v>257</v>
       </c>
       <c r="M67" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="N67" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="O67" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80496_hackney", ".\export_data\inspection_reports\80496_hackney")</f>
@@ -8891,28 +8894,28 @@
     </row>
     <row r="68" spans="1:20">
       <c r="A68" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B68" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C68" t="s">
         <v>217</v>
       </c>
       <c r="D68" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E68" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="F68" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="G68" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="I68" t="s">
         <v>78</v>
@@ -8924,7 +8927,7 @@
         <v>223</v>
       </c>
       <c r="L68" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="M68" t="s">
         <v>171</v>
@@ -8954,28 +8957,28 @@
     </row>
     <row r="69" spans="1:20">
       <c r="A69" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B69" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C69" t="s">
         <v>217</v>
       </c>
       <c r="D69" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E69" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="F69" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="G69" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="I69" t="s">
         <v>78</v>
@@ -8990,10 +8993,10 @@
         <v>212</v>
       </c>
       <c r="M69" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="N69" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="O69" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80498_haringey", ".\export_data\inspection_reports\80498_haringey")</f>
@@ -9017,28 +9020,28 @@
     </row>
     <row r="70" spans="1:20">
       <c r="A70" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B70" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C70" t="s">
         <v>217</v>
       </c>
       <c r="D70" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="E70" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="F70" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="G70" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="I70" t="s">
         <v>189</v>
@@ -9053,10 +9056,10 @@
         <v>341</v>
       </c>
       <c r="M70" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="N70" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="O70" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80499_harrow", ".\export_data\inspection_reports\80499_harrow")</f>
@@ -9080,28 +9083,28 @@
     </row>
     <row r="71" spans="1:20">
       <c r="A71" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="B71" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C71" t="s">
         <v>217</v>
       </c>
       <c r="D71" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="E71" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="F71" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="G71" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="I71" t="s">
         <v>189</v>
@@ -9110,16 +9113,16 @@
         <v>48</v>
       </c>
       <c r="K71" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="L71" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="M71" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="N71" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="O71" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80500_havering", ".\export_data\inspection_reports\80500_havering")</f>
@@ -9143,28 +9146,28 @@
     </row>
     <row r="72" spans="1:20">
       <c r="A72" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B72" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C72" t="s">
         <v>217</v>
       </c>
       <c r="D72" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="E72" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="F72" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="G72" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="I72" t="s">
         <v>78</v>
@@ -9176,13 +9179,13 @@
         <v>223</v>
       </c>
       <c r="L72" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="M72" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="N72" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="O72" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80501_hillingdon", ".\export_data\inspection_reports\80501_hillingdon")</f>
@@ -9206,28 +9209,28 @@
     </row>
     <row r="73" spans="1:20">
       <c r="A73" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B73" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C73" t="s">
         <v>217</v>
       </c>
       <c r="D73" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="E73" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="F73" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G73" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="I73" t="s">
         <v>8</v>
@@ -9239,13 +9242,13 @@
         <v>139</v>
       </c>
       <c r="L73" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="M73" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="N73" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="O73" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80503_hounslow", ".\export_data\inspection_reports\80503_hounslow")</f>
@@ -9269,28 +9272,28 @@
     </row>
     <row r="74" spans="1:20">
       <c r="A74" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B74" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="C74" t="s">
         <v>217</v>
       </c>
       <c r="D74" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="E74" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="F74" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="G74" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="I74" t="s">
         <v>78</v>
@@ -9305,7 +9308,7 @@
         <v>95</v>
       </c>
       <c r="M74" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="N74" t="s">
         <v>97</v>
@@ -9332,28 +9335,28 @@
     </row>
     <row r="75" spans="1:20">
       <c r="A75" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B75" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C75" t="s">
         <v>217</v>
       </c>
       <c r="D75" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="E75" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="F75" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="G75" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="I75" t="s">
         <v>8</v>
@@ -9362,7 +9365,7 @@
         <v>48</v>
       </c>
       <c r="K75" t="s">
-        <v>742</v>
+        <v>379</v>
       </c>
       <c r="L75" t="s">
         <v>212</v>
@@ -9371,7 +9374,7 @@
         <v>213</v>
       </c>
       <c r="N75" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="O75" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80506_lambeth", ".\export_data\inspection_reports\80506_lambeth")</f>
@@ -9390,33 +9393,33 @@
         <v>78</v>
       </c>
       <c r="T75" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="76" spans="1:20">
       <c r="A76" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B76" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C76" t="s">
         <v>217</v>
       </c>
       <c r="D76" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="E76" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="F76" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="G76" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="I76" t="s">
         <v>8</v>
@@ -9425,16 +9428,16 @@
         <v>48</v>
       </c>
       <c r="K76" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="L76" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="M76" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="N76" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="O76" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80508_lewisham", ".\export_data\inspection_reports\80508_lewisham")</f>
@@ -9458,28 +9461,28 @@
     </row>
     <row r="77" spans="1:20">
       <c r="A77" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B77" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C77" t="s">
         <v>217</v>
       </c>
       <c r="D77" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="E77" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="F77" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="G77" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="I77" t="s">
         <v>78</v>
@@ -9488,7 +9491,7 @@
         <v>9</v>
       </c>
       <c r="K77" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="L77" t="s">
         <v>37</v>
@@ -9521,28 +9524,28 @@
     </row>
     <row r="78" spans="1:20">
       <c r="A78" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B78" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C78" t="s">
         <v>217</v>
       </c>
       <c r="D78" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="E78" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="F78" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="G78" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="I78" t="s">
         <v>78</v>
@@ -9557,7 +9560,7 @@
         <v>460</v>
       </c>
       <c r="M78" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="N78" t="s">
         <v>462</v>
@@ -9584,28 +9587,28 @@
     </row>
     <row r="79" spans="1:20">
       <c r="A79" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B79" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C79" t="s">
         <v>217</v>
       </c>
       <c r="D79" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="E79" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="F79" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="G79" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="I79" t="s">
         <v>78</v>
@@ -9614,16 +9617,16 @@
         <v>9</v>
       </c>
       <c r="K79" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="L79" t="s">
+        <v>440</v>
+      </c>
+      <c r="M79" t="s">
         <v>441</v>
       </c>
-      <c r="M79" t="s">
+      <c r="N79" t="s">
         <v>442</v>
-      </c>
-      <c r="N79" t="s">
-        <v>443</v>
       </c>
       <c r="O79" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80512_redbridge", ".\export_data\inspection_reports\80512_redbridge")</f>
@@ -9642,33 +9645,33 @@
         <v>78</v>
       </c>
       <c r="T79" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="80" spans="1:20">
       <c r="A80" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B80" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C80" t="s">
         <v>217</v>
       </c>
       <c r="D80" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="E80" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="F80" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="G80" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="I80" t="s">
         <v>78</v>
@@ -9710,28 +9713,28 @@
     </row>
     <row r="81" spans="1:20">
       <c r="A81" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B81" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C81" t="s">
         <v>217</v>
       </c>
       <c r="D81" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="E81" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="F81" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="G81" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="I81" t="s">
         <v>8</v>
@@ -9740,7 +9743,7 @@
         <v>9</v>
       </c>
       <c r="K81" t="s">
-        <v>742</v>
+        <v>379</v>
       </c>
       <c r="L81" t="s">
         <v>278</v>
@@ -9768,33 +9771,33 @@
         <v>8</v>
       </c>
       <c r="T81" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="82" spans="1:20">
       <c r="A82" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B82" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C82" t="s">
         <v>217</v>
       </c>
       <c r="D82" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="E82" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="F82" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="G82" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="I82" t="s">
         <v>8</v>
@@ -9806,7 +9809,7 @@
         <v>62</v>
       </c>
       <c r="L82" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="M82" t="s">
         <v>151</v>
@@ -9836,28 +9839,28 @@
     </row>
     <row r="83" spans="1:20">
       <c r="A83" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B83" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C83" t="s">
         <v>217</v>
       </c>
       <c r="D83" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="E83" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="F83" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="G83" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="I83" t="s">
         <v>78</v>
@@ -9869,13 +9872,13 @@
         <v>24</v>
       </c>
       <c r="L83" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="M83" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="N83" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="O83" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80516_tower hamlets", ".\export_data\inspection_reports\80516_tower hamlets")</f>
@@ -9899,28 +9902,28 @@
     </row>
     <row r="84" spans="1:20">
       <c r="A84" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B84" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C84" t="s">
         <v>217</v>
       </c>
       <c r="D84" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="E84" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="F84" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="G84" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="I84" t="s">
         <v>8</v>
@@ -9929,16 +9932,16 @@
         <v>9</v>
       </c>
       <c r="K84" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="L84" t="s">
         <v>508</v>
       </c>
       <c r="M84" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="N84" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="O84" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80517_waltham forest", ".\export_data\inspection_reports\80517_waltham forest")</f>
@@ -9962,28 +9965,28 @@
     </row>
     <row r="85" spans="1:20">
       <c r="A85" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B85" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C85" t="s">
         <v>217</v>
       </c>
       <c r="D85" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="E85" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="F85" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="G85" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="I85" t="s">
         <v>78</v>
@@ -9992,13 +9995,13 @@
         <v>9</v>
       </c>
       <c r="K85" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="L85" t="s">
         <v>499</v>
       </c>
       <c r="M85" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="N85" t="s">
         <v>280</v>
@@ -10025,28 +10028,28 @@
     </row>
     <row r="86" spans="1:20">
       <c r="A86" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B86" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C86" t="s">
         <v>217</v>
       </c>
       <c r="D86" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E86" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="F86" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="G86" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="I86" t="s">
         <v>78</v>
@@ -10058,13 +10061,13 @@
         <v>106</v>
       </c>
       <c r="L86" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="M86" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="N86" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="O86" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80519_westminster", ".\export_data\inspection_reports\80519_westminster")</f>
@@ -10088,28 +10091,28 @@
     </row>
     <row r="87" spans="1:20">
       <c r="A87" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B87" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C87" t="s">
         <v>31</v>
       </c>
       <c r="D87" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="E87" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="F87" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="G87" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="I87" t="s">
         <v>8</v>
@@ -10121,13 +10124,13 @@
         <v>150</v>
       </c>
       <c r="L87" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="M87" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="N87" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="O87" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80520_luton", ".\export_data\inspection_reports\80520_luton")</f>
@@ -10151,28 +10154,28 @@
     </row>
     <row r="88" spans="1:20">
       <c r="A88" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B88" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C88" t="s">
         <v>56</v>
       </c>
       <c r="D88" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="E88" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="F88" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="G88" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="I88" t="s">
         <v>78</v>
@@ -10184,13 +10187,13 @@
         <v>277</v>
       </c>
       <c r="L88" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="M88" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="N88" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="O88" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80521_manchester", ".\export_data\inspection_reports\80521_manchester")</f>
@@ -10214,28 +10217,28 @@
     </row>
     <row r="89" spans="1:20">
       <c r="A89" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B89" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C89" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D89" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="E89" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="F89" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="G89" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="I89" t="s">
         <v>8</v>
@@ -10247,13 +10250,13 @@
         <v>24</v>
       </c>
       <c r="L89" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="M89" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="N89" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="O89" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80522_medway", ".\export_data\inspection_reports\80522_medway")</f>
@@ -10277,28 +10280,28 @@
     </row>
     <row r="90" spans="1:20">
       <c r="A90" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B90" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C90" t="s">
         <v>293</v>
       </c>
       <c r="D90" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="E90" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="F90" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="G90" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="I90" t="s">
         <v>73</v>
@@ -10307,7 +10310,7 @@
         <v>48</v>
       </c>
       <c r="K90" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="L90" t="s">
         <v>75</v>
@@ -10340,28 +10343,28 @@
     </row>
     <row r="91" spans="1:20">
       <c r="A91" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B91" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C91" t="s">
         <v>100</v>
       </c>
       <c r="D91" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="E91" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="F91" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="G91" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="I91" t="s">
         <v>8</v>
@@ -10370,16 +10373,16 @@
         <v>48</v>
       </c>
       <c r="K91" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="L91" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="M91" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="N91" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="O91" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80524_milton keynes", ".\export_data\inspection_reports\80524_milton keynes")</f>
@@ -10398,33 +10401,33 @@
         <v>78</v>
       </c>
       <c r="T91" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="92" spans="1:20">
       <c r="A92" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B92" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C92" t="s">
         <v>293</v>
       </c>
       <c r="D92" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="E92" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="F92" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="G92" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="I92" t="s">
         <v>8</v>
@@ -10436,13 +10439,13 @@
         <v>245</v>
       </c>
       <c r="L92" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="M92" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="N92" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="O92" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80525_newcastle upon tyne", ".\export_data\inspection_reports\80525_newcastle upon tyne")</f>
@@ -10466,28 +10469,28 @@
     </row>
     <row r="93" spans="1:20">
       <c r="A93" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B93" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C93" t="s">
         <v>31</v>
       </c>
       <c r="D93" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="E93" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="F93" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="G93" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="I93" t="s">
         <v>78</v>
@@ -10496,13 +10499,13 @@
         <v>9</v>
       </c>
       <c r="K93" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="L93" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="M93" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="N93" t="s">
         <v>280</v>
@@ -10524,33 +10527,33 @@
         <v>78</v>
       </c>
       <c r="T93" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="94" spans="1:20">
       <c r="A94" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B94" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C94" t="s">
         <v>2</v>
       </c>
       <c r="D94" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="E94" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="F94" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="G94" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="I94" t="s">
         <v>8</v>
@@ -10565,10 +10568,10 @@
         <v>37</v>
       </c>
       <c r="M94" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="N94" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="O94" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80526_north east lincolnshire", ".\export_data\inspection_reports\80526_north east lincolnshire")</f>
@@ -10592,28 +10595,28 @@
     </row>
     <row r="95" spans="1:20">
       <c r="A95" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B95" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C95" t="s">
         <v>2</v>
       </c>
       <c r="D95" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="E95" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="F95" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="G95" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="I95" t="s">
         <v>78</v>
@@ -10625,13 +10628,13 @@
         <v>507</v>
       </c>
       <c r="L95" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="M95" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="N95" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="O95" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80527_north lincolnshire", ".\export_data\inspection_reports\80527_north lincolnshire")</f>
@@ -10655,28 +10658,28 @@
     </row>
     <row r="96" spans="1:20">
       <c r="A96" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B96" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C96" t="s">
         <v>304</v>
       </c>
       <c r="D96" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="E96" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="F96" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="G96" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="I96" t="s">
         <v>73</v>
@@ -10685,7 +10688,7 @@
         <v>48</v>
       </c>
       <c r="K96" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="L96" t="s">
         <v>527</v>
@@ -10718,28 +10721,28 @@
     </row>
     <row r="97" spans="1:20">
       <c r="A97" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B97" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C97" t="s">
         <v>18</v>
       </c>
       <c r="D97" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="E97" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="F97" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="G97" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="I97" t="s">
         <v>14</v>
@@ -10751,13 +10754,13 @@
         <v>10</v>
       </c>
       <c r="L97" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="M97" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="N97" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="O97" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80528_north somerset", ".\export_data\inspection_reports\80528_north somerset")</f>
@@ -10781,28 +10784,28 @@
     </row>
     <row r="98" spans="1:20">
       <c r="A98" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B98" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C98" t="s">
         <v>293</v>
       </c>
       <c r="D98" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="E98" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="F98" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="G98" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="I98" t="s">
         <v>78</v>
@@ -10814,13 +10817,13 @@
         <v>371</v>
       </c>
       <c r="L98" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="M98" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="N98" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="O98" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80529_north tyneside", ".\export_data\inspection_reports\80529_north tyneside")</f>
@@ -10844,28 +10847,28 @@
     </row>
     <row r="99" spans="1:20">
       <c r="A99" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B99" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="C99" t="s">
         <v>2</v>
       </c>
       <c r="D99" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="E99" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="F99" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="G99" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="I99" t="s">
         <v>78</v>
@@ -10874,16 +10877,16 @@
         <v>9</v>
       </c>
       <c r="K99" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="L99" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="M99" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="N99" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="O99" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80530_north yorkshire", ".\export_data\inspection_reports\80530_north yorkshire")</f>
@@ -10907,28 +10910,28 @@
     </row>
     <row r="100" spans="1:20">
       <c r="A100" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B100" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="C100" t="s">
         <v>293</v>
       </c>
       <c r="D100" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="E100" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="F100" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="G100" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="I100" t="s">
         <v>78</v>
@@ -10937,16 +10940,16 @@
         <v>9</v>
       </c>
       <c r="K100" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="L100" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="M100" t="s">
+        <v>430</v>
+      </c>
+      <c r="N100" t="s">
         <v>431</v>
-      </c>
-      <c r="N100" t="s">
-        <v>432</v>
       </c>
       <c r="O100" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80532_northumberland", ".\export_data\inspection_reports\80532_northumberland")</f>
@@ -10965,33 +10968,33 @@
         <v>8</v>
       </c>
       <c r="T100" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="101" spans="1:20">
       <c r="A101" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B101" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C101" t="s">
         <v>304</v>
       </c>
       <c r="D101" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="E101" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="F101" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="G101" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="I101" t="s">
         <v>189</v>
@@ -11000,10 +11003,10 @@
         <v>117</v>
       </c>
       <c r="K101" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="N101" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="O101" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80533_nottingham", ".\export_data\inspection_reports\80533_nottingham")</f>
@@ -11022,33 +11025,33 @@
         <v>189</v>
       </c>
       <c r="T101" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="102" spans="1:20">
       <c r="A102" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B102" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C102" t="s">
         <v>304</v>
       </c>
       <c r="D102" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="E102" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="F102" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="G102" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="I102" t="s">
         <v>8</v>
@@ -11057,16 +11060,16 @@
         <v>9</v>
       </c>
       <c r="K102" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="L102" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="M102" t="s">
+        <v>430</v>
+      </c>
+      <c r="N102" t="s">
         <v>431</v>
-      </c>
-      <c r="N102" t="s">
-        <v>432</v>
       </c>
       <c r="O102" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80534_nottinghamshire", ".\export_data\inspection_reports\80534_nottinghamshire")</f>
@@ -11090,28 +11093,28 @@
     </row>
     <row r="103" spans="1:20">
       <c r="A103" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B103" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C103" t="s">
         <v>56</v>
       </c>
       <c r="D103" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="E103" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F103" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="G103" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="I103" t="s">
         <v>8</v>
@@ -11123,13 +11126,13 @@
         <v>516</v>
       </c>
       <c r="L103" t="s">
+        <v>429</v>
+      </c>
+      <c r="M103" t="s">
         <v>430</v>
       </c>
-      <c r="M103" t="s">
+      <c r="N103" t="s">
         <v>431</v>
-      </c>
-      <c r="N103" t="s">
-        <v>432</v>
       </c>
       <c r="O103" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80535_oldham", ".\export_data\inspection_reports\80535_oldham")</f>
@@ -11153,28 +11156,28 @@
     </row>
     <row r="104" spans="1:20">
       <c r="A104" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B104" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="C104" t="s">
         <v>100</v>
       </c>
       <c r="D104" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="E104" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="F104" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="G104" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="I104" t="s">
         <v>8</v>
@@ -11183,16 +11186,16 @@
         <v>48</v>
       </c>
       <c r="K104" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="L104" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="M104" t="s">
         <v>161</v>
       </c>
       <c r="N104" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="O104" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80536_oxfordshire", ".\export_data\inspection_reports\80536_oxfordshire")</f>
@@ -11216,28 +11219,28 @@
     </row>
     <row r="105" spans="1:20">
       <c r="A105" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B105" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C105" t="s">
         <v>31</v>
       </c>
       <c r="D105" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="E105" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="F105" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="G105" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="I105" t="s">
         <v>189</v>
@@ -11246,16 +11249,16 @@
         <v>48</v>
       </c>
       <c r="K105" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="L105" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="M105" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="N105" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="O105" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80537_peterborough", ".\export_data\inspection_reports\80537_peterborough")</f>
@@ -11274,33 +11277,33 @@
         <v>189</v>
       </c>
       <c r="T105" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="106" spans="1:20">
       <c r="A106" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B106" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C106" t="s">
         <v>18</v>
       </c>
       <c r="D106" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="E106" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="F106" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="G106" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="I106" t="s">
         <v>14</v>
@@ -11312,13 +11315,13 @@
         <v>128</v>
       </c>
       <c r="L106" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="M106" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="N106" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="O106" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80538_plymouth", ".\export_data\inspection_reports\80538_plymouth")</f>
@@ -11342,28 +11345,28 @@
     </row>
     <row r="107" spans="1:20">
       <c r="A107" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B107" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="C107" t="s">
         <v>100</v>
       </c>
       <c r="D107" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="E107" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="F107" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="G107" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="I107" t="s">
         <v>73</v>
@@ -11372,16 +11375,16 @@
         <v>9</v>
       </c>
       <c r="K107" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="L107" t="s">
         <v>361</v>
       </c>
       <c r="M107" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="N107" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="O107" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80539_portsmouth", ".\export_data\inspection_reports\80539_portsmouth")</f>
@@ -11400,33 +11403,33 @@
         <v>78</v>
       </c>
       <c r="T107" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="108" spans="1:20">
       <c r="A108" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B108" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="C108" t="s">
         <v>100</v>
       </c>
       <c r="D108" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="E108" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="F108" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="G108" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="I108" t="s">
         <v>14</v>
@@ -11444,7 +11447,7 @@
         <v>555</v>
       </c>
       <c r="N108" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="O108" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80540_reading", ".\export_data\inspection_reports\80540_reading")</f>
@@ -11468,28 +11471,28 @@
     </row>
     <row r="109" spans="1:20">
       <c r="A109" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B109" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C109" t="s">
         <v>293</v>
       </c>
       <c r="D109" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="E109" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="F109" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="G109" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="I109" t="s">
         <v>8</v>
@@ -11501,7 +11504,7 @@
         <v>245</v>
       </c>
       <c r="L109" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="M109" t="s">
         <v>108</v>
@@ -11531,28 +11534,28 @@
     </row>
     <row r="110" spans="1:20">
       <c r="A110" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B110" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C110" t="s">
         <v>56</v>
       </c>
       <c r="D110" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="E110" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="F110" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="G110" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="I110" t="s">
         <v>14</v>
@@ -11564,13 +11567,13 @@
         <v>86</v>
       </c>
       <c r="L110" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="M110" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="N110" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="O110" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80542_rochdale", ".\export_data\inspection_reports\80542_rochdale")</f>
@@ -11594,28 +11597,28 @@
     </row>
     <row r="111" spans="1:20">
       <c r="A111" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B111" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="C111" t="s">
         <v>2</v>
       </c>
       <c r="D111" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="E111" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="F111" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="G111" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="I111" t="s">
         <v>78</v>
@@ -11633,7 +11636,7 @@
         <v>490</v>
       </c>
       <c r="N111" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="O111" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80543_rotherham", ".\export_data\inspection_reports\80543_rotherham")</f>
@@ -11657,28 +11660,28 @@
     </row>
     <row r="112" spans="1:20">
       <c r="A112" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B112" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="C112" t="s">
         <v>217</v>
       </c>
       <c r="D112" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="E112" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="F112" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G112" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="I112" t="s">
         <v>78</v>
@@ -11690,13 +11693,13 @@
         <v>139</v>
       </c>
       <c r="L112" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="M112" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="N112" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="O112" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80544_kensington and chelsea", ".\export_data\inspection_reports\80544_kensington and chelsea")</f>
@@ -11720,28 +11723,28 @@
     </row>
     <row r="113" spans="1:20">
       <c r="A113" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B113" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="C113" t="s">
         <v>217</v>
       </c>
       <c r="D113" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="E113" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="F113" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="G113" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="I113" t="s">
         <v>78</v>
@@ -11750,13 +11753,13 @@
         <v>9</v>
       </c>
       <c r="K113" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="L113" t="s">
         <v>95</v>
       </c>
       <c r="M113" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="N113" t="s">
         <v>97</v>
@@ -11783,28 +11786,28 @@
     </row>
     <row r="114" spans="1:20">
       <c r="A114" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B114" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="C114" t="s">
         <v>100</v>
       </c>
       <c r="D114" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="E114" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="F114" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="G114" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="I114" t="s">
         <v>8</v>
@@ -11813,7 +11816,7 @@
         <v>9</v>
       </c>
       <c r="K114" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="L114" t="s">
         <v>288</v>
@@ -11822,7 +11825,7 @@
         <v>331</v>
       </c>
       <c r="N114" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="O114" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80546_windsor &amp; maidenhead", ".\export_data\inspection_reports\80546_windsor &amp; maidenhead")</f>
@@ -11846,28 +11849,28 @@
     </row>
     <row r="115" spans="1:20">
       <c r="A115" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B115" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="C115" t="s">
         <v>304</v>
       </c>
       <c r="D115" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="E115" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="F115" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="G115" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="I115" t="s">
         <v>8</v>
@@ -11879,13 +11882,13 @@
         <v>507</v>
       </c>
       <c r="L115" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="M115" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="N115" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="O115" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80547_rutland", ".\export_data\inspection_reports\80547_rutland")</f>
@@ -11909,28 +11912,28 @@
     </row>
     <row r="116" spans="1:20">
       <c r="A116" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B116" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="C116" t="s">
         <v>56</v>
       </c>
       <c r="D116" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="E116" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="F116" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="G116" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="I116" t="s">
         <v>8</v>
@@ -11939,10 +11942,10 @@
         <v>9</v>
       </c>
       <c r="K116" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="L116" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="M116" t="s">
         <v>321</v>
@@ -11967,33 +11970,33 @@
         <v>78</v>
       </c>
       <c r="T116" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="117" spans="1:20">
       <c r="A117" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B117" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="C117" t="s">
         <v>42</v>
       </c>
       <c r="D117" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E117" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="F117" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="G117" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="I117" t="s">
         <v>8</v>
@@ -12002,16 +12005,16 @@
         <v>48</v>
       </c>
       <c r="K117" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="L117" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="M117" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="N117" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="O117" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80549_sandwell", ".\export_data\inspection_reports\80549_sandwell")</f>
@@ -12035,28 +12038,28 @@
     </row>
     <row r="118" spans="1:20">
       <c r="A118" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B118" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="C118" t="s">
         <v>56</v>
       </c>
       <c r="D118" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="E118" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="F118" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="G118" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="I118" t="s">
         <v>8</v>
@@ -12068,7 +12071,7 @@
         <v>86</v>
       </c>
       <c r="L118" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="M118" t="s">
         <v>538</v>
@@ -12098,28 +12101,28 @@
     </row>
     <row r="119" spans="1:20">
       <c r="A119" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B119" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="C119" t="s">
         <v>2</v>
       </c>
       <c r="D119" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="E119" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="F119" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="G119" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="I119" t="s">
         <v>8</v>
@@ -12134,10 +12137,10 @@
         <v>11</v>
       </c>
       <c r="M119" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N119" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="O119" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80551_sheffield", ".\export_data\inspection_reports\80551_sheffield")</f>
@@ -12161,28 +12164,28 @@
     </row>
     <row r="120" spans="1:20">
       <c r="A120" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B120" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="C120" t="s">
         <v>42</v>
       </c>
       <c r="D120" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="E120" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="F120" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="G120" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="I120" t="s">
         <v>78</v>
@@ -12191,10 +12194,10 @@
         <v>48</v>
       </c>
       <c r="K120" t="s">
-        <v>742</v>
+        <v>379</v>
       </c>
       <c r="L120" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="M120" t="s">
         <v>538</v>
@@ -12219,33 +12222,33 @@
         <v>8</v>
       </c>
       <c r="T120" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="121" spans="1:20">
       <c r="A121" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B121" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="C121" t="s">
         <v>100</v>
       </c>
       <c r="D121" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="E121" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="F121" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="G121" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="I121" t="s">
         <v>73</v>
@@ -12254,7 +12257,7 @@
         <v>48</v>
       </c>
       <c r="K121" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="L121" t="s">
         <v>361</v>
@@ -12287,28 +12290,28 @@
     </row>
     <row r="122" spans="1:20">
       <c r="A122" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B122" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="C122" t="s">
         <v>42</v>
       </c>
       <c r="D122" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="E122" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="F122" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="G122" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="I122" t="s">
         <v>8</v>
@@ -12317,13 +12320,13 @@
         <v>48</v>
       </c>
       <c r="K122" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="L122" t="s">
         <v>489</v>
       </c>
       <c r="M122" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="N122" t="s">
         <v>462</v>
@@ -12345,33 +12348,33 @@
         <v>8</v>
       </c>
       <c r="T122" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="123" spans="1:20">
       <c r="A123" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B123" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="C123" t="s">
         <v>18</v>
       </c>
       <c r="D123" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="E123" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F123" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="G123" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="I123" t="s">
         <v>73</v>
@@ -12383,13 +12386,13 @@
         <v>200</v>
       </c>
       <c r="L123" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="M123" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="N123" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="O123" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80555_somerset", ".\export_data\inspection_reports\80555_somerset")</f>
@@ -12413,28 +12416,28 @@
     </row>
     <row r="124" spans="1:20">
       <c r="A124" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B124" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="C124" t="s">
         <v>18</v>
       </c>
       <c r="D124" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="E124" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="F124" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="G124" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="I124" t="s">
         <v>8</v>
@@ -12446,13 +12449,13 @@
         <v>10</v>
       </c>
       <c r="L124" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="M124" t="s">
+        <v>441</v>
+      </c>
+      <c r="N124" t="s">
         <v>442</v>
-      </c>
-      <c r="N124" t="s">
-        <v>443</v>
       </c>
       <c r="O124" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80556_south gloucestershire", ".\export_data\inspection_reports\80556_south gloucestershire")</f>
@@ -12476,28 +12479,28 @@
     </row>
     <row r="125" spans="1:20">
       <c r="A125" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B125" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="C125" t="s">
         <v>293</v>
       </c>
       <c r="D125" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="E125" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="F125" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="G125" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="I125" t="s">
         <v>73</v>
@@ -12509,13 +12512,13 @@
         <v>62</v>
       </c>
       <c r="L125" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="M125" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="N125" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="O125" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80557_south tyneside", ".\export_data\inspection_reports\80557_south tyneside")</f>
@@ -12539,28 +12542,28 @@
     </row>
     <row r="126" spans="1:20">
       <c r="A126" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B126" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="C126" t="s">
         <v>100</v>
       </c>
       <c r="D126" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="E126" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="F126" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="G126" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="I126" t="s">
         <v>8</v>
@@ -12569,16 +12572,16 @@
         <v>48</v>
       </c>
       <c r="K126" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L126" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="M126" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="N126" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="O126" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80558_southampton", ".\export_data\inspection_reports\80558_southampton")</f>
@@ -12597,33 +12600,33 @@
         <v>8</v>
       </c>
       <c r="T126" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="127" spans="1:20">
       <c r="A127" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B127" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="C127" t="s">
         <v>31</v>
       </c>
       <c r="D127" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="E127" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="F127" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="G127" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="I127" t="s">
         <v>8</v>
@@ -12635,13 +12638,13 @@
         <v>74</v>
       </c>
       <c r="L127" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="M127" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="N127" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="O127" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80559_southend-on-sea", ".\export_data\inspection_reports\80559_southend-on-sea")</f>
@@ -12665,28 +12668,28 @@
     </row>
     <row r="128" spans="1:20">
       <c r="A128" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="B128" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C128" t="s">
         <v>56</v>
       </c>
       <c r="D128" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="E128" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="F128" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="G128" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="I128" t="s">
         <v>8</v>
@@ -12695,7 +12698,7 @@
         <v>48</v>
       </c>
       <c r="K128" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="L128" t="s">
         <v>581</v>
@@ -12723,33 +12726,33 @@
         <v>8</v>
       </c>
       <c r="T128" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="129" spans="1:20">
       <c r="A129" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B129" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="C129" t="s">
         <v>42</v>
       </c>
       <c r="D129" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="E129" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="F129" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="G129" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="I129" t="s">
         <v>14</v>
@@ -12761,7 +12764,7 @@
         <v>200</v>
       </c>
       <c r="L129" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="M129" t="s">
         <v>321</v>
@@ -12791,28 +12794,28 @@
     </row>
     <row r="130" spans="1:20">
       <c r="A130" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B130" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="C130" t="s">
         <v>56</v>
       </c>
       <c r="D130" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="E130" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="F130" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="G130" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="I130" t="s">
         <v>14</v>
@@ -12821,16 +12824,16 @@
         <v>48</v>
       </c>
       <c r="K130" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L130" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="M130" t="s">
         <v>311</v>
       </c>
       <c r="N130" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="O130" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80562_stockport", ".\export_data\inspection_reports\80562_stockport")</f>
@@ -12849,33 +12852,33 @@
         <v>8</v>
       </c>
       <c r="T130" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="131" spans="1:20">
       <c r="A131" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="B131" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="C131" t="s">
         <v>293</v>
       </c>
       <c r="D131" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="E131" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="F131" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="G131" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="I131" t="s">
         <v>14</v>
@@ -12884,16 +12887,16 @@
         <v>48</v>
       </c>
       <c r="K131" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="L131" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="M131" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="N131" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="O131" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80563_stockton-on-tees", ".\export_data\inspection_reports\80563_stockton-on-tees")</f>
@@ -12917,28 +12920,28 @@
     </row>
     <row r="132" spans="1:20">
       <c r="A132" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="B132" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="C132" t="s">
         <v>42</v>
       </c>
       <c r="D132" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="E132" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="F132" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="G132" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="I132" t="s">
         <v>14</v>
@@ -12950,13 +12953,13 @@
         <v>49</v>
       </c>
       <c r="L132" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="M132" t="s">
         <v>311</v>
       </c>
       <c r="N132" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="O132" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80564_stoke-on-trent", ".\export_data\inspection_reports\80564_stoke-on-trent")</f>
@@ -12980,28 +12983,28 @@
     </row>
     <row r="133" spans="1:20">
       <c r="A133" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B133" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="C133" t="s">
         <v>31</v>
       </c>
       <c r="D133" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="E133" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="F133" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="G133" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="I133" t="s">
         <v>14</v>
@@ -13013,13 +13016,13 @@
         <v>179</v>
       </c>
       <c r="L133" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="M133" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="N133" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="O133" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80565_suffolk", ".\export_data\inspection_reports\80565_suffolk")</f>
@@ -13043,28 +13046,28 @@
     </row>
     <row r="134" spans="1:20">
       <c r="A134" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B134" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="C134" t="s">
         <v>293</v>
       </c>
       <c r="D134" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="E134" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="F134" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="G134" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="I134" t="s">
         <v>78</v>
@@ -13073,7 +13076,7 @@
         <v>9</v>
       </c>
       <c r="K134" t="s">
-        <v>379</v>
+        <v>450</v>
       </c>
       <c r="L134" t="s">
         <v>140</v>
@@ -13082,7 +13085,7 @@
         <v>342</v>
       </c>
       <c r="N134" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="O134" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80566_sunderland", ".\export_data\inspection_reports\80566_sunderland")</f>
@@ -13101,33 +13104,33 @@
         <v>8</v>
       </c>
       <c r="T134" t="s">
-        <v>15</v>
+        <v>432</v>
       </c>
     </row>
     <row r="135" spans="1:20">
       <c r="A135" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B135" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="C135" t="s">
         <v>100</v>
       </c>
       <c r="D135" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="E135" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="F135" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="G135" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="I135" t="s">
         <v>8</v>
@@ -13169,28 +13172,28 @@
     </row>
     <row r="136" spans="1:20">
       <c r="A136" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="B136" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="C136" t="s">
         <v>18</v>
       </c>
       <c r="D136" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="E136" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="F136" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="G136" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="I136" t="s">
         <v>189</v>
@@ -13202,13 +13205,13 @@
         <v>139</v>
       </c>
       <c r="L136" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="M136" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="N136" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="O136" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80568_swindon", ".\export_data\inspection_reports\80568_swindon")</f>
@@ -13232,28 +13235,28 @@
     </row>
     <row r="137" spans="1:20">
       <c r="A137" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B137" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="C137" t="s">
         <v>56</v>
       </c>
       <c r="D137" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="E137" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="F137" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="G137" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="I137" t="s">
         <v>189</v>
@@ -13265,13 +13268,13 @@
         <v>117</v>
       </c>
       <c r="L137" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="M137" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="N137" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="O137" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80569_tameside", ".\export_data\inspection_reports\80569_tameside")</f>
@@ -13295,28 +13298,28 @@
     </row>
     <row r="138" spans="1:20">
       <c r="A138" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B138" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="C138" t="s">
         <v>42</v>
       </c>
       <c r="D138" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="E138" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="F138" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="G138" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="I138" t="s">
         <v>78</v>
@@ -13328,13 +13331,13 @@
         <v>179</v>
       </c>
       <c r="L138" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="M138" t="s">
         <v>555</v>
       </c>
       <c r="N138" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="O138" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80570_telford &amp; wrekin", ".\export_data\inspection_reports\80570_telford &amp; wrekin")</f>
@@ -13358,28 +13361,28 @@
     </row>
     <row r="139" spans="1:20">
       <c r="A139" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="B139" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="C139" t="s">
         <v>31</v>
       </c>
       <c r="D139" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="E139" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="F139" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="G139" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="I139" t="s">
         <v>78</v>
@@ -13391,13 +13394,13 @@
         <v>507</v>
       </c>
       <c r="L139" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="M139" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="N139" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="O139" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80571_thurrock", ".\export_data\inspection_reports\80571_thurrock")</f>
@@ -13421,28 +13424,28 @@
     </row>
     <row r="140" spans="1:20">
       <c r="A140" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B140" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="C140" t="s">
         <v>18</v>
       </c>
       <c r="D140" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="E140" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="F140" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="G140" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="I140" t="s">
         <v>8</v>
@@ -13457,10 +13460,10 @@
         <v>212</v>
       </c>
       <c r="M140" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="N140" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="O140" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80572_torbay", ".\export_data\inspection_reports\80572_torbay")</f>
@@ -13479,33 +13482,33 @@
         <v>8</v>
       </c>
       <c r="T140" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="141" spans="1:20">
       <c r="A141" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="B141" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="C141" t="s">
         <v>56</v>
       </c>
       <c r="D141" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="E141" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="F141" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="G141" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="I141" t="s">
         <v>73</v>
@@ -13514,7 +13517,7 @@
         <v>48</v>
       </c>
       <c r="K141" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="L141" t="s">
         <v>75</v>
@@ -13523,7 +13526,7 @@
         <v>76</v>
       </c>
       <c r="N141" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="O141" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80573_trafford", ".\export_data\inspection_reports\80573_trafford")</f>
@@ -13547,28 +13550,28 @@
     </row>
     <row r="142" spans="1:20">
       <c r="A142" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="B142" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="C142" t="s">
         <v>42</v>
       </c>
       <c r="D142" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="E142" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="F142" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="G142" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="I142" t="s">
         <v>78</v>
@@ -13580,10 +13583,10 @@
         <v>139</v>
       </c>
       <c r="L142" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="M142" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="N142" t="s">
         <v>312</v>
@@ -13610,28 +13613,28 @@
     </row>
     <row r="143" spans="1:20">
       <c r="A143" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="B143" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="C143" t="s">
         <v>56</v>
       </c>
       <c r="D143" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="E143" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="F143" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="G143" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="I143" t="s">
         <v>8</v>
@@ -13643,13 +13646,13 @@
         <v>86</v>
       </c>
       <c r="L143" t="s">
+        <v>440</v>
+      </c>
+      <c r="M143" t="s">
         <v>441</v>
       </c>
-      <c r="M143" t="s">
-        <v>442</v>
-      </c>
       <c r="N143" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="O143" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80575_warrington", ".\export_data\inspection_reports\80575_warrington")</f>
@@ -13673,28 +13676,28 @@
     </row>
     <row r="144" spans="1:20">
       <c r="A144" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B144" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="C144" t="s">
         <v>42</v>
       </c>
       <c r="D144" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="E144" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="F144" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="G144" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="I144" t="s">
         <v>14</v>
@@ -13706,13 +13709,13 @@
         <v>117</v>
       </c>
       <c r="L144" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="M144" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="N144" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="O144" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80576_warwickshire", ".\export_data\inspection_reports\80576_warwickshire")</f>
@@ -13736,28 +13739,28 @@
     </row>
     <row r="145" spans="1:20">
       <c r="A145" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="B145" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="C145" t="s">
         <v>100</v>
       </c>
       <c r="D145" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="E145" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="F145" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="G145" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="I145" t="s">
         <v>8</v>
@@ -13766,16 +13769,16 @@
         <v>9</v>
       </c>
       <c r="K145" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="L145" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="M145" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="N145" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="O145" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80577_west berkshire", ".\export_data\inspection_reports\80577_west berkshire")</f>
@@ -13794,33 +13797,33 @@
         <v>8</v>
       </c>
       <c r="T145" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="146" spans="1:20">
       <c r="A146" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="B146" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="C146" t="s">
         <v>304</v>
       </c>
       <c r="D146" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="E146" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="F146" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="G146" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="I146" t="s">
         <v>73</v>
@@ -13862,28 +13865,28 @@
     </row>
     <row r="147" spans="1:20">
       <c r="A147" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="B147" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="C147" t="s">
         <v>100</v>
       </c>
       <c r="D147" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="E147" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="F147" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="G147" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="I147" t="s">
         <v>14</v>
@@ -13892,16 +13895,16 @@
         <v>48</v>
       </c>
       <c r="K147" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="L147" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="M147" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="N147" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="O147" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80578_west sussex", ".\export_data\inspection_reports\80578_west sussex")</f>
@@ -13925,28 +13928,28 @@
     </row>
     <row r="148" spans="1:20">
       <c r="A148" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B148" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="C148" t="s">
         <v>56</v>
       </c>
       <c r="D148" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="E148" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="F148" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="G148" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="I148" t="s">
         <v>8</v>
@@ -13955,7 +13958,7 @@
         <v>48</v>
       </c>
       <c r="K148" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="L148" t="s">
         <v>554</v>
@@ -13964,7 +13967,7 @@
         <v>555</v>
       </c>
       <c r="N148" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="O148" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\2733698_westmorland and furness", ".\export_data\inspection_reports\2733698_westmorland and furness")</f>
@@ -13983,33 +13986,33 @@
         <v>14</v>
       </c>
       <c r="T148" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="149" spans="1:20">
       <c r="A149" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="B149" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C149" t="s">
         <v>56</v>
       </c>
       <c r="D149" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="E149" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="F149" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="G149" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="I149" t="s">
         <v>8</v>
@@ -14018,16 +14021,16 @@
         <v>48</v>
       </c>
       <c r="K149" t="s">
-        <v>742</v>
+        <v>379</v>
       </c>
       <c r="L149" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="M149" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="N149" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="O149" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80579_wigan", ".\export_data\inspection_reports\80579_wigan")</f>
@@ -14046,33 +14049,33 @@
         <v>78</v>
       </c>
       <c r="T149" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="150" spans="1:20">
       <c r="A150" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B150" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="C150" t="s">
         <v>18</v>
       </c>
       <c r="D150" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="E150" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="F150" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="G150" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="I150" t="s">
         <v>78</v>
@@ -14081,16 +14084,16 @@
         <v>9</v>
       </c>
       <c r="K150" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="L150" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="M150" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="N150" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="O150" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80580_wiltshire", ".\export_data\inspection_reports\80580_wiltshire")</f>
@@ -14114,28 +14117,28 @@
     </row>
     <row r="151" spans="1:20">
       <c r="A151" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="B151" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="C151" t="s">
         <v>56</v>
       </c>
       <c r="D151" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="E151" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="F151" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="G151" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="I151" t="s">
         <v>14</v>
@@ -14147,13 +14150,13 @@
         <v>190</v>
       </c>
       <c r="L151" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="M151" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="N151" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="O151" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80581_wirral", ".\export_data\inspection_reports\80581_wirral")</f>
@@ -14177,28 +14180,28 @@
     </row>
     <row r="152" spans="1:20">
       <c r="A152" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="B152" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="C152" t="s">
         <v>100</v>
       </c>
       <c r="D152" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="E152" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="F152" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="G152" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="I152" t="s">
         <v>14</v>
@@ -14207,16 +14210,16 @@
         <v>48</v>
       </c>
       <c r="K152" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L152" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="M152" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="N152" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="O152" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80582_wokingham", ".\export_data\inspection_reports\80582_wokingham")</f>
@@ -14235,33 +14238,33 @@
         <v>14</v>
       </c>
       <c r="T152" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="153" spans="1:20">
       <c r="A153" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="B153" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="C153" t="s">
         <v>42</v>
       </c>
       <c r="D153" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="E153" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="F153" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="G153" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="I153" t="s">
         <v>8</v>
@@ -14273,13 +14276,13 @@
         <v>200</v>
       </c>
       <c r="L153" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="M153" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="N153" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="O153" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80583_wolverhampton", ".\export_data\inspection_reports\80583_wolverhampton")</f>
@@ -14303,28 +14306,28 @@
     </row>
     <row r="154" spans="1:20">
       <c r="A154" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="B154" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="C154" t="s">
         <v>42</v>
       </c>
       <c r="D154" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="E154" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="F154" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="G154" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="I154" t="s">
         <v>8</v>
@@ -14336,13 +14339,13 @@
         <v>179</v>
       </c>
       <c r="L154" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="M154" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="N154" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="O154" s="3">
         <f>HYPERLINK(".\.\export_data\inspection_reports\80584_worcestershire", ".\export_data\inspection_reports\80584_worcestershire")</f>
